--- a/docs/api/api-spec-final.xlsx
+++ b/docs/api/api-spec-final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. v3 팀원 피드백 API 수정" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 전체 API 명세 v3" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Sprint 우선순위 분류" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 공통 규칙 v2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 비동기 처리 흐름" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 평가요건 매핑" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 담당자 역할 기준" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 변경 이력" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="0. v3 팀원 피드백 API 수정" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. 전체 API 명세 v3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Sprint 우선순위 분류" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. 공통 규칙 v2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. 비동기 처리 흐름" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. 평가요건 매핑" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. 담당자 역할 기준" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. 변경 이력" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,119 +575,119 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>팀원 피드백</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>API 변경 내역</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 마이페이지 요구사항 신규 추가</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>PATCH /api/v1/users/me/password 신규 추가 (P0)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/users/me/consents 신규 추가 (P0)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>REQ-AUTH-002 로그인 메시지 보안 강화</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/auth/login Error Response 비고 업데이트</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>REQ-REC-001 이미지 보관 90일 확정</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/records 비고는 이미 90일로 명시 (변경 불필요)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001 약품 카드 제조사 포함</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/records/{record_id}/ocr 응답 스키마에 manufacturer 명시</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 제조사 무조건 표기</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search, /drugs/{id} 응답 스키마에 manufacturer 필수 명시</t>
         </is>
@@ -701,81 +701,81 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>관련 요구사항</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 / P0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 / P0</t>
         </is>
@@ -789,102 +789,102 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>v3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>전체 API 개수</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>47개</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>49개 (+2)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0 API</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>29개</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>31개 (+2 마이페이지)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>마이페이지 도메인</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>GET/PATCH/DELETE /users/me (3개)</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>+ PATCH password + GET consents (5개)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>로그인 보안</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>구분 메시지</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>통합 메시지 (계정 존재 노출 방지)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>약품 응답</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>제조사 선택적</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>manufacturer 필수 필드 명시</t>
         </is>
@@ -899,119 +899,119 @@
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>변경 내용</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>관련 API</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 — 메뉴 10개·비밀번호 변경 4단계·회원탈퇴 5단계 상세 명시</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>(요구사항 정의서 본문)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>비밀번호 변경 API 비고 보강 (4단계 흐름, 5회 실패 10분 제한, 모든 기기 로그아웃)</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>회원탈퇴 API 비고 보강 (5단계 흐름, 5회 실패 24시간 제한, OCR/LLM cancelled, 30일 영구 삭제)</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>DELETE /users/me</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="26">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>약관 동의 조회 API 비고 보강 (5개 약관 + 전문 보기 링크)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="26">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>닉네임 수정 API 비고 보강 (30일 1회 제한, 욕설 필터링)</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="26">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>선택 약관 토글 API 신규 추가 (마케팅 수신 동의/철회)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/consents/{consent_type} ⭐ 신규</t>
         </is>
@@ -2034,132 +2034,132 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" s="26">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>기능 단계</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>도메인</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>API명</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>Request URL</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>HTTP Method</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>인증 필요</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>비동기 여부</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="35" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t>Header Schema</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="35" t="inlineStr">
         <is>
           <t>Query Parameter Schema</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="35" t="inlineStr">
         <is>
           <t>Request Body Example</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="35" t="inlineStr">
         <is>
           <t>Success Response Example</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="35" t="inlineStr">
         <is>
           <t>Error Response / Status Code</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R4" s="35" t="inlineStr">
         <is>
           <t>관련 ERD 테이블</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="35" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="35" t="inlineStr">
         <is>
           <t>완료 상태</t>
         </is>
       </c>
     </row>
     <row r="5" ht="127.5" customHeight="1" s="26">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>회원가입 및 필수 동의 저장</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/signup</t>
         </is>
@@ -2169,38 +2169,38 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>이메일 회원가입과 필수 약관/민감정보/AI 분석 동의를 한 번에 저장한다.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t>Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t>{
   "email": "user@example.com",
@@ -2228,7 +2228,7 @@
 }</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t>{
   "user_id": 1,
@@ -2237,52 +2237,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 필수값 누락 / 409 이메일 중복</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="33" t="inlineStr">
         <is>
           <t>users, user_consents</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t>이메일 형식, 비밀번호 정책 검증 포함</t>
         </is>
       </c>
-      <c r="T5" s="27" t="inlineStr">
+      <c r="T5" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>로그인 및 토큰 발급</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/login</t>
         </is>
@@ -2292,38 +2292,38 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>로그인 성공 시 access_token과 refresh_token을 발급한다.</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="33" t="inlineStr">
         <is>
           <t>Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t>{
   "email": "user@example.com",
@@ -2331,7 +2331,7 @@
 }</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t>{
   "access_token": "jwt.access",
@@ -2344,7 +2344,7 @@
 }</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 입력 오류
@@ -2352,47 +2352,47 @@
 429 5회 연속 실패 잠금</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr">
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>users, auth_tokens</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="S6" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 팀원 피드백: 개인정보 보안 — 401 응답 시 계정 없음/비밀번호 불일치 구분 없이 통합 메시지</t>
         </is>
       </c>
-      <c r="T6" s="27" t="inlineStr">
+      <c r="T6" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/logout</t>
         </is>
@@ -2402,93 +2402,93 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>현재 refresh token을 revoke 처리한다.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="N7" s="33" t="n"/>
+      <c r="O7" s="33" t="inlineStr">
         <is>
           <t>{
   "refresh_token": "jwt.refresh"
 }</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "로그아웃되었습니다."
 }</t>
         </is>
       </c>
-      <c r="Q7" s="11" t="inlineStr">
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R7" s="11" t="inlineStr">
+      <c r="R7" s="33" t="inlineStr">
         <is>
           <t>auth_tokens</t>
         </is>
       </c>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="27" t="inlineStr">
+      <c r="S7" s="33" t="n"/>
+      <c r="T7" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>내 정보 조회</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me</t>
         </is>
@@ -2498,39 +2498,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>로그인한 사용자의 기본 정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L8" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="N8" s="33" t="n"/>
+      <c r="O8" s="33" t="n"/>
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t>{
   "user_id": 1,
@@ -2541,48 +2541,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q8" s="11" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R8" s="11" t="inlineStr">
+      <c r="R8" s="33" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="27" t="inlineStr">
+      <c r="S8" s="33" t="n"/>
+      <c r="T8" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="9" ht="63.75" customHeight="1" s="26">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>건강정보</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 저장/수정</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
@@ -2592,39 +2592,39 @@
           <t>PUT</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드와 챗봇 context에 사용할 최소 건강정보를 저장한다.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="L9" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="N9" s="33" t="n"/>
+      <c r="O9" s="33" t="inlineStr">
         <is>
           <t>{
   "age_group": "30s",
@@ -2643,7 +2643,7 @@
 }</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P9" s="33" t="inlineStr">
         <is>
           <t>{
   "profile_id": 1,
@@ -2651,48 +2651,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 잘못된 입력 / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R9" s="11" t="inlineStr">
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>user_health_profiles</t>
         </is>
       </c>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="27" t="inlineStr">
+      <c r="S9" s="33" t="n"/>
+      <c r="T9" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="26">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>건강정보</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 조회</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
@@ -2702,39 +2702,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>현재 로그인 사용자의 건강정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="N10" s="33" t="n"/>
+      <c r="O10" s="33" t="n"/>
+      <c r="P10" s="33" t="inlineStr">
         <is>
           <t>{
   "profile_id": 1,
@@ -2750,48 +2750,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="inlineStr">
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 404 프로필 없음</t>
         </is>
       </c>
-      <c r="R10" s="11" t="inlineStr">
+      <c r="R10" s="33" t="inlineStr">
         <is>
           <t>user_health_profiles</t>
         </is>
       </c>
-      <c r="S10" s="11" t="n"/>
-      <c r="T10" s="27" t="inlineStr">
+      <c r="S10" s="33" t="n"/>
+      <c r="T10" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="26">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>의료 이미지 업로드</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
@@ -2801,45 +2801,45 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>처방전/약봉투/진료기록 이미지 또는 PDF를 업로드하고 record_id를 생성한다.</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="L11" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: multipart/form-data</t>
         </is>
       </c>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="N11" s="33" t="n"/>
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t>file: binary
 record_type: prescription|medicine_bag|medical_record</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -2850,52 +2850,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">201 Created / 400 파일 형식 오류 / 401 인증 실패 / 413 용량 초과 </t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
+      <c r="R11" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="33" t="inlineStr">
         <is>
           <t>image_expires_at 90일 보존 정책 반영 | ⭐ v3: 요구사항 REQ-REC-001과 90일 정책 일치 확인 완료 (팀원 피드백)</t>
         </is>
       </c>
-      <c r="T11" s="27" t="inlineStr">
+      <c r="T11" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1" s="26">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>진료기록 목록 조회</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
@@ -2905,43 +2905,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>사용자의 업로드 기록 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="33" t="inlineStr">
         <is>
           <t>page, size, record_type</t>
         </is>
       </c>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="O12" s="33" t="n"/>
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -2957,48 +2957,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="Q12" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R12" s="11" t="inlineStr">
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="27" t="inlineStr">
+      <c r="S12" s="33" t="n"/>
+      <c r="T12" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" s="26">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>진료기록 상세 조회</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}</t>
         </is>
@@ -3008,90 +3008,100 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>record_id 기준으로 업로드 정보와 처리 상태를 조회한다.</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K13" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L13" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="N13" s="33" t="n"/>
+      <c r="O13" s="33" t="n"/>
+      <c r="P13" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
   "record_type": "prescription",
   "status": "ocr_completed",
-  "ocr_confidence": 0.91
+  "file_url": "https://.../rx.png",
+  "file_name": "처방전.png",
+  "file_size": 123456,
+  "content_type": "image/png",
+  "ocr_text": "...",
+  "ocr_edited_text": null,
+  "ocr_confidence": 0.91,
+  "input_method": "upload",
+  "image_expires_at": "2026-09-01T00:00:00Z",
+  "uploaded_at": "2026-06-04T10:00:00Z",
+  "updated_at": "2026-06-04T10:05:00Z"
 }</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="inlineStr">
+      <c r="Q13" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 타 사용자 기록 접근 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R13" s="11" t="inlineStr">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="27" t="inlineStr">
+      <c r="S13" s="33" t="n"/>
+      <c r="T13" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" s="26">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>OCR 작업 시작</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>/api/v1/ocr/jobs</t>
         </is>
@@ -3101,39 +3111,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>업로드된 record_id에 대해 OCR 비동기 작업을 시작하고 job_id를 반환한다.</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="N14" s="33" t="n"/>
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3141,7 +3151,7 @@
 }</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P14" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 101,
@@ -3151,52 +3161,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t>202 Accepted / 400 잘못된 record_id / 401 인증 실패 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R14" s="11" t="inlineStr">
+      <c r="R14" s="33" t="inlineStr">
         <is>
           <t>processing_jobs, medical_records</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="S14" s="33" t="inlineStr">
         <is>
           <t>P95 3초 대응을 위해 job_id 반환 방식</t>
         </is>
       </c>
-      <c r="T14" s="27" t="inlineStr">
+      <c r="T14" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="26">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 조회</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-result</t>
         </is>
@@ -3206,39 +3216,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>OCR 원문, 편집본, 신뢰도, 약품 후보를 조회한다.</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L15" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="N15" s="33" t="n"/>
+      <c r="O15" s="33" t="n"/>
+      <c r="P15" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3255,52 +3265,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 타 사용자 기록 접근 / 404 결과 없음</t>
         </is>
       </c>
-      <c r="R15" s="11" t="inlineStr">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>medical_records, medications</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="S15" s="33" t="inlineStr">
         <is>
           <t>⭐ v3: 응답에 medications[].manufacturer 필수 포함 (팀원 피드백)</t>
         </is>
       </c>
-      <c r="T15" s="27" t="inlineStr">
+      <c r="T15" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="26">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 수정</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-text</t>
         </is>
@@ -3310,46 +3320,46 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>사용자가 OCR 결과를 확인/수정하고 저장한다.</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="N16" s="33" t="n"/>
+      <c r="O16" s="33" t="inlineStr">
         <is>
           <t>{
   "ocr_edited_text": "타이레놀 500mg 1정 식후 복용"
 }</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P16" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3358,48 +3368,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="Q16" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 입력값 오류 / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R16" s="11" t="inlineStr">
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="27" t="inlineStr">
+      <c r="S16" s="33" t="n"/>
+      <c r="T16" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1" s="26">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>OCR 약품명 확인</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/medications/{medication_id}/verify</t>
         </is>
@@ -3409,39 +3419,39 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>OCR 신뢰도 낮은 약품명을 사용자가 확인하고 is_verified를 true로 저장한다.</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K17" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L17" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="N17" s="33" t="n"/>
+      <c r="O17" s="33" t="inlineStr">
         <is>
           <t>{
   "drug_name": "타이레놀정500mg",
@@ -3449,7 +3459,7 @@
 }</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P17" s="33" t="inlineStr">
         <is>
           <t>{
   "medication_id": 30,
@@ -3458,52 +3468,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="inlineStr">
+      <c r="Q17" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 입력 오류 / 401 인증 실패 / 404 약품 없음</t>
         </is>
       </c>
-      <c r="R17" s="11" t="inlineStr">
+      <c r="R17" s="33" t="inlineStr">
         <is>
           <t>medications</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="33" t="inlineStr">
         <is>
           <t>신뢰도 기준 미만 후보를 사용자 확인 대상으로 표시</t>
         </is>
       </c>
-      <c r="T17" s="27" t="inlineStr">
+      <c r="T17" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1" s="26">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>식약처 약품 검색</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/search</t>
         </is>
@@ -3513,43 +3523,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>약품명, 일반명, 성분명 기준으로 식약처 API 또는 캐시에서 약품을 검색한다.</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>부분 비동기</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="L18" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N18" s="33" t="inlineStr">
         <is>
           <t>q, search_type, page, size</t>
         </is>
       </c>
-      <c r="O18" s="11" t="n"/>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="O18" s="33" t="n"/>
+      <c r="P18" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -3563,52 +3573,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q18" s="11" t="inlineStr">
+      <c r="Q18" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 검색어 누락 / 401 인증 실패 / 504 외부 API timeout</t>
         </is>
       </c>
-      <c r="R18" s="11" t="inlineStr">
+      <c r="R18" s="33" t="inlineStr">
         <is>
           <t>drug_references, drug_caches, api_failure_logs</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="33" t="inlineStr">
         <is>
           <t>⭐ 식약처 의약품안전나라 (공공데이터포털): https://www.data.go.kr/data/15095677/openapi.do | 일반명↔상품명 양방향 검색, 캐시 7일 | ⭐ v3: 응답 스키마에 manufacturer 필수 필드 (누락 시 "제조사 정보 없음")</t>
         </is>
       </c>
-      <c r="T18" s="27" t="inlineStr">
+      <c r="T18" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1" s="26">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>약품 상세 조회</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/{drug_id}</t>
         </is>
@@ -3618,39 +3628,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>식약처 기준 약품 상세 정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="N19" s="33" t="n"/>
+      <c r="O19" s="33" t="n"/>
+      <c r="P19" s="33" t="inlineStr">
         <is>
           <t>{
   "drug_ref_id": 100,
@@ -3662,52 +3672,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="inlineStr">
+      <c r="Q19" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 404 약품 없음</t>
         </is>
       </c>
-      <c r="R19" s="11" t="inlineStr">
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>drug_references</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="S19" s="33" t="inlineStr">
         <is>
           <t>⭐ 식약처 의약품 제품 허가정보. 제조사 정보 포함 응답 | ⭐ v3: manufacturer 필수 필드 명시</t>
         </is>
       </c>
-      <c r="T19" s="27" t="inlineStr">
+      <c r="T19" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1" s="26">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>기록별 약품 목록 조회</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/medications</t>
         </is>
@@ -3717,39 +3727,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>OCR 또는 직접 입력으로 추출/저장된 약품 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L20" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="M20" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="11" t="n"/>
-      <c r="P20" s="11" t="inlineStr">
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3765,52 +3775,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q20" s="11" t="inlineStr">
+      <c r="Q20" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R20" s="11" t="inlineStr">
+      <c r="R20" s="33" t="inlineStr">
         <is>
           <t>medications</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>⭐ v4: 미구현 — ocr-result의 medication_candidates로 대체 추정 (확인 필요)</t>
+      <c r="S20" s="33" t="inlineStr">
+        <is>
+          <t>구현 완료 (Backend B). 응답 {record_id, medications:[{medication_id, drug_name, dosage, frequency, timing, duration, is_verified, ...}]}</t>
         </is>
       </c>
       <c r="T20" s="28" t="inlineStr">
         <is>
-          <t>미구현 (확인필요)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1" s="26">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>LLM 복약/생활습관 가이드 생성</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/generate</t>
         </is>
@@ -3820,39 +3830,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="33" t="inlineStr">
         <is>
           <t>OCR 수정본, 약품 정보, 건강정보를 context로 LLM 가이드 생성 작업을 시작한다.</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L21" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M21" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="N21" s="33" t="n"/>
+      <c r="O21" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3860,7 +3870,7 @@
 }</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P21" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 201,
@@ -3869,53 +3879,53 @@
 }</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="inlineStr">
+      <c r="Q21" s="33" t="inlineStr">
         <is>
           <t>202 Accepted / 400 입력 오류 / 401 인증 실패 / 404 record 없음 / 504 LLM timeout</t>
         </is>
       </c>
-      <c r="R21" s="11" t="inlineStr">
+      <c r="R21" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items, processing_jobs</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="S21" s="33" t="inlineStr">
         <is>
           <t>model_name, prompt_version 저장
 ⭐ v4: 실제 경로 /guides → /guides/generate 반영</t>
         </is>
       </c>
-      <c r="T21" s="27" t="inlineStr">
+      <c r="T21" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="22" ht="63.75" customHeight="1" s="26">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>가이드 상세 조회</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/{guide_id}</t>
         </is>
@@ -3925,39 +3935,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>생성된 복약/생활습관 가이드와 항목별 guide_items를 조회한다.</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="11" t="n"/>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="33" t="inlineStr">
         <is>
           <t>{
   "guide_id": 50,
@@ -3977,48 +3987,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q22" s="11" t="inlineStr">
+      <c r="Q22" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 가이드 없음</t>
         </is>
       </c>
-      <c r="R22" s="11" t="inlineStr">
+      <c r="R22" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items</t>
         </is>
       </c>
-      <c r="S22" s="11" t="n"/>
-      <c r="T22" s="27" t="inlineStr">
+      <c r="S22" s="33" t="n"/>
+      <c r="T22" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1" s="26">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>기록별 최신 가이드 조회</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/guide</t>
         </is>
@@ -4028,39 +4038,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>record_id 기준 최신 가이드 결과를 조회한다.</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="L23" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="N23" s="33" t="n"/>
+      <c r="O23" s="33" t="n"/>
+      <c r="P23" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -4070,52 +4080,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="inlineStr">
+      <c r="Q23" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 가이드 없음</t>
         </is>
       </c>
-      <c r="R23" s="11" t="inlineStr">
+      <c r="R23" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items</t>
         </is>
       </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>⭐ v4: 미구현 — GET /guides/{guide_id}로 대체 (확인 필요)</t>
+      <c r="S23" s="33" t="inlineStr">
+        <is>
+          <t>구현 완료 (#104, Backend B). 응답은 GET /guides/{guide_id}와 동일 (GenerateGuideResponse)</t>
         </is>
       </c>
       <c r="T23" s="28" t="inlineStr">
         <is>
-          <t>미구현 (확인필요)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1" s="26">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>상담 세션 생성</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
@@ -4125,39 +4135,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>record_id 또는 guide_id와 연결된 상담 세션을 생성한다.</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L24" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="11" t="inlineStr">
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -4166,7 +4176,7 @@
 }</t>
         </is>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P24" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4175,48 +4185,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q24" s="11" t="inlineStr">
+      <c r="Q24" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 입력 오류 / 401 인증 실패 / 403 권한 없음</t>
         </is>
       </c>
-      <c r="R24" s="11" t="inlineStr">
+      <c r="R24" s="33" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="27" t="inlineStr">
+      <c r="S24" s="33" t="n"/>
+      <c r="T24" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1" s="26">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>상담 세션 목록 조회</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
@@ -4226,43 +4236,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="33" t="inlineStr">
         <is>
           <t>로그인 사용자의 상담 세션 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L25" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="M25" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N25" s="33" t="inlineStr">
         <is>
           <t>offset, limit</t>
         </is>
       </c>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="inlineStr">
+      <c r="O25" s="33" t="n"/>
+      <c r="P25" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -4291,48 +4301,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="inlineStr">
+      <c r="Q25" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R25" s="11" t="inlineStr">
+      <c r="R25" s="33" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="27" t="inlineStr">
+      <c r="S25" s="33" t="n"/>
+      <c r="T25" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="26" ht="63.75" customHeight="1" s="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>상담 메시지 목록 조회</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
@@ -4342,43 +4352,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="33" t="inlineStr">
         <is>
           <t>특정 상담 세션의 메시지를 시간순으로 조회한다.</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="L26" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="M26" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N26" s="11" t="inlineStr">
+      <c r="N26" s="33" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="O26" s="11" t="n"/>
-      <c r="P26" s="11" t="inlineStr">
+      <c r="O26" s="33" t="n"/>
+      <c r="P26" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4406,48 +4416,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q26" s="11" t="inlineStr">
+      <c r="Q26" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 세션 없음</t>
         </is>
       </c>
-      <c r="R26" s="11" t="inlineStr">
+      <c r="R26" s="33" t="inlineStr">
         <is>
           <t>chat_sessions, chat_messages</t>
         </is>
       </c>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="27" t="inlineStr">
+      <c r="S26" s="33" t="n"/>
+      <c r="T26" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="27" ht="63.75" customHeight="1" s="26">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>챗봇 메시지 전송 및 답변 생성</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
@@ -4457,39 +4467,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>사용자 질문을 저장하고 최근 3~5개 메시지를 context로 LLM 또는 규칙 기반 답변을 생성한다.</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L27" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M27" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="N27" s="33" t="n"/>
+      <c r="O27" s="33" t="inlineStr">
         <is>
           <t>{
   "message": "이 약을 식후에 먹어도 되나요?",
@@ -4498,7 +4508,7 @@
 }</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P27" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4509,52 +4519,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="Q27" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 질문 누락 / 401 인증 실패 / 403 권한 없음 / 429 요청 횟수 초과 / ※ LLM 실패는 job status=failed로 처리</t>
         </is>
       </c>
-      <c r="R27" s="11" t="inlineStr">
+      <c r="R27" s="33" t="inlineStr">
         <is>
           <t>chat_messages, chat_sessions</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="S27" s="33" t="inlineStr">
         <is>
           <t>위험 질문은 safety_flag=true 및 의료기관 상담 권고</t>
         </is>
       </c>
-      <c r="T27" s="27" t="inlineStr">
+      <c r="T27" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1" s="26">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>작업 상태</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>비동기 작업 상태 조회</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>/api/v1/processing-jobs/{job_id}</t>
         </is>
@@ -4564,39 +4574,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>OCR, 약품 조회, 가이드 생성 등 비동기 작업 상태를 조회한다.</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L28" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M28" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="N28" s="33" t="n"/>
+      <c r="O28" s="33" t="n"/>
+      <c r="P28" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 101,
@@ -4609,48 +4619,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="inlineStr">
+      <c r="Q28" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 job 없음</t>
         </is>
       </c>
-      <c r="R28" s="11" t="inlineStr">
+      <c r="R28" s="33" t="inlineStr">
         <is>
           <t>processing_jobs</t>
         </is>
       </c>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="27" t="inlineStr">
+      <c r="S28" s="33" t="n"/>
+      <c r="T28" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1" s="26">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>복약 가이드 피드백 단순 등록</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>/api/v1/feedbacks</t>
         </is>
@@ -4660,39 +4670,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="33" t="inlineStr">
         <is>
           <t>가이드 또는 챗봇 답변에 대한 별점/코멘트를 등록한다.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M29" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="N29" s="33" t="n"/>
+      <c r="O29" s="33" t="inlineStr">
         <is>
           <t>{
   "guide_id": 50,
@@ -4703,7 +4713,7 @@
 }</t>
         </is>
       </c>
-      <c r="P29" s="11" t="inlineStr">
+      <c r="P29" s="33" t="inlineStr">
         <is>
           <t>{
   "feedback_id": 300,
@@ -4711,17 +4721,17 @@
 }</t>
         </is>
       </c>
-      <c r="Q29" s="11" t="inlineStr">
+      <c r="Q29" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 입력 오류 / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R29" s="11" t="inlineStr">
+      <c r="R29" s="33" t="inlineStr">
         <is>
           <t>feedbacks</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr">
+      <c r="S29" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 멘토 반영: P1 → P0 상향 (가이드·챗봇 피드백 등록 필수 MVP)
 ⭐ v4: 미구현(미착수) — 구현 여부 확인 필요</t>
@@ -4734,30 +4744,30 @@
       </c>
     </row>
     <row r="30" ht="60" customHeight="1" s="26">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>알림 목록 조회</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications</t>
         </is>
@@ -4767,43 +4777,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>사용자 알림 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="L30" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="M30" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr">
+      <c r="N30" s="33" t="inlineStr">
         <is>
           <t>page, size, is_read</t>
         </is>
       </c>
-      <c r="O30" s="11" t="n"/>
-      <c r="P30" s="11" t="inlineStr">
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -4816,52 +4826,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q30" s="11" t="inlineStr">
+      <c r="Q30" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R30" s="11" t="inlineStr">
+      <c r="R30" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="S30" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 멘토 반영: P2 → P0 상향 (내부 알림함 필수 MVP)</t>
         </is>
       </c>
-      <c r="T30" s="27" t="inlineStr">
+      <c r="T30" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1" s="26">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>미읽음 알림 개수 조회</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/unread-count</t>
         </is>
@@ -4871,91 +4881,91 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>대시보드 알림 아이콘 뱃지에 표시할 미읽음 알림 개수를 반환한다.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="L31" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="M31" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="N31" s="33" t="n"/>
+      <c r="O31" s="33" t="n"/>
+      <c r="P31" s="33" t="inlineStr">
         <is>
           <t>{
   "unread_count": 5
 }</t>
         </is>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
+      <c r="Q31" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R31" s="11" t="inlineStr">
+      <c r="R31" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="S31" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백): 대시보드 미읽음 뱃지용</t>
         </is>
       </c>
-      <c r="T31" s="27" t="inlineStr">
+      <c r="T31" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1" s="26">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>알림 읽음 처리</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}/read</t>
         </is>
@@ -4965,39 +4975,39 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>사용자가 알림을 클릭하거나 모두 읽음 처리할 때 read 상태로 변경한다.</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L32" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="M32" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-      <c r="P32" s="11" t="inlineStr">
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="33" t="inlineStr">
         <is>
           <t>{
   "notification_id": 12,
@@ -5006,52 +5016,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q32" s="11" t="inlineStr">
+      <c r="Q32" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 알림 없음</t>
         </is>
       </c>
-      <c r="R32" s="11" t="inlineStr">
+      <c r="R32" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="S32" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백)</t>
         </is>
       </c>
-      <c r="T32" s="27" t="inlineStr">
+      <c r="T32" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1" s="26">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}</t>
         </is>
@@ -5061,61 +5071,61 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="33" t="inlineStr">
         <is>
           <t>사용자가 개별 알림을 삭제한다.</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J33" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="L33" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr">
+      <c r="M33" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="11" t="inlineStr">
+      <c r="N33" s="33" t="n"/>
+      <c r="O33" s="33" t="n"/>
+      <c r="P33" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "삭제되었습니다."
 }</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="Q33" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 알림 없음</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
+      <c r="R33" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백)</t>
         </is>
       </c>
-      <c r="T33" s="27" t="inlineStr">
+      <c r="T33" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -6941,30 +6951,30 @@
       </c>
     </row>
     <row r="52" ht="180" customHeight="1" s="26">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
@@ -6974,38 +6984,38 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="33" t="inlineStr">
         <is>
           <t>사용자가 마이페이지에서 비밀번호를 변경한다. 현재 비밀번호 확인 후 새 비밀번호로 변경. 변경 성공 시 모든 기기에서 로그아웃 처리.</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="K52" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="L52" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr">
+      <c r="M52" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N52" s="11" t="n"/>
-      <c r="O52" s="11" t="inlineStr">
+      <c r="N52" s="33" t="n"/>
+      <c r="O52" s="33" t="inlineStr">
         <is>
           <t>{
   "current_password": "OldP@ssw0rd1",
@@ -7013,7 +7023,7 @@
 }</t>
         </is>
       </c>
-      <c r="P52" s="11" t="inlineStr">
+      <c r="P52" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "비밀번호가 변경되었습니다. 다시 로그인해주세요.",
@@ -7021,54 +7031,54 @@
 }</t>
         </is>
       </c>
-      <c r="Q52" s="11" t="inlineStr">
+      <c r="Q52" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 입력 오류 (정책 미충족, 현재 비밀번호와 동일)
 401 현재 비밀번호 불일치</t>
         </is>
       </c>
-      <c r="R52" s="11" t="inlineStr">
+      <c r="R52" s="33" t="inlineStr">
         <is>
           <t>users, auth_tokens</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001). 정책: 8자 이상 20자 이하, 영문 대소문자/숫자/특수문자 중 3종류 이상. ⭐ v3 업데이트: 4단계 흐름 (현재 비밀번호 → 새 비밀번호 → 확인 → 완료). 현재 비밀번호 5회 실패 시 10분 제한. 이메일·이름·닉네임과 동일하면 변경 제한. 변경 성공 시 모든 refresh_token revoke (전체 기기 강제 로그아웃)</t>
         </is>
       </c>
-      <c r="T52" s="27" t="inlineStr">
+      <c r="T52" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="53" ht="180" customHeight="1" s="26">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="33" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D53" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
@@ -7078,39 +7088,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="33" t="inlineStr">
         <is>
           <t>사용자가 가입 시 동의한 약관·개인정보 처리방침·민감 건강정보 수집·AI 분석 활용·마케팅 등 동의 내역을 조회한다.</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I53" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J53" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="K53" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L53" s="11" t="inlineStr">
+      <c r="L53" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="M53" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="inlineStr">
+      <c r="N53" s="33" t="n"/>
+      <c r="O53" s="33" t="n"/>
+      <c r="P53" s="33" t="inlineStr">
         <is>
           <t>{
   "consents": [
@@ -7148,53 +7158,53 @@
 }</t>
         </is>
       </c>
-      <c r="Q53" s="11" t="inlineStr">
+      <c r="Q53" s="33" t="inlineStr">
         <is>
           <t>200 OK
 401 인증 실패</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr">
+      <c r="R53" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr">
+      <c r="S53" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001). 마이페이지 &gt; 약관 동의 내역 화면용. 5개 약관 (terms, privacy, health_data, ai_analysis, marketing) 각각 상태·동의 일시 반환. 각 약관마다 "전문 보기" 링크 제공</t>
         </is>
       </c>
-      <c r="T53" s="27" t="inlineStr">
+      <c r="T53" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="54" ht="199.5" customHeight="1" s="26">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>약관 동의 토글 (선택 약관)</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents/{consent_type}</t>
         </is>
@@ -7204,49 +7214,49 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="H54" s="33" t="inlineStr">
         <is>
           <t>사용자가 마이페이지에서 선택 약관(현재 marketing만 해당)의 동의/철회를 토글한다. 필수 약관(terms, privacy, health_data, ai_analysis)은 본 API로 변경 불가. 필수 약관 철회는 회원탈퇴(DELETE /users/me)를 통해서만 가능.</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="I54" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K54" s="11" t="inlineStr">
+      <c r="K54" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L54" s="11" t="inlineStr">
+      <c r="L54" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M54" s="11" t="inlineStr">
+      <c r="M54" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N54" s="11" t="inlineStr">
+      <c r="N54" s="33" t="inlineStr">
         <is>
           <t>path: consent_type (marketing)</t>
         </is>
       </c>
-      <c r="O54" s="11" t="inlineStr">
+      <c r="O54" s="33" t="inlineStr">
         <is>
           <t>{
   "is_agreed": true
 }</t>
         </is>
       </c>
-      <c r="P54" s="11" t="inlineStr">
+      <c r="P54" s="33" t="inlineStr">
         <is>
           <t>{
   "consent_type": "marketing",
@@ -7256,7 +7266,7 @@
 }</t>
         </is>
       </c>
-      <c r="Q54" s="11" t="inlineStr">
+      <c r="Q54" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 필수 약관은 본 API로 변경 불가 ("필수 약관 철회는 회원탈퇴를 진행해주세요")
@@ -7264,17 +7274,17 @@
 404 존재하지 않는 consent_type</t>
         </is>
       </c>
-      <c r="R54" s="11" t="inlineStr">
+      <c r="R54" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr">
+      <c r="S54" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001 자세히 작성). 마케팅 수신 동의 토글용. 필수 약관(terms·privacy·health_data·ai_analysis)은 400 응답 후 회원탈퇴 안내</t>
         </is>
       </c>
-      <c r="T54" s="27" t="inlineStr">
+      <c r="T54" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -9264,52 +9274,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9319,32 +9329,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/signup</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>회원가입 및 필수 동의 저장</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9354,32 +9364,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/login</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>로그인 및 토큰 발급</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9389,32 +9399,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/logout</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9424,32 +9434,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>내 정보 조회</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9459,32 +9469,32 @@
           <t>PUT</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 저장/수정</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9494,32 +9504,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 조회</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9529,32 +9539,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>의료 이미지 업로드</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9564,32 +9574,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>진료기록 목록 조회</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9599,32 +9609,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>진료기록 상세 조회</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9634,32 +9644,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>/api/v1/ocr/jobs</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>OCR 작업 시작</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9669,32 +9679,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-result</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 조회</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9704,32 +9714,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-text</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 수정</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9739,32 +9749,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/medications/{medication_id}/verify</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>OCR 약품명 확인</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9774,32 +9784,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/search</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>식약처 약품 검색</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9809,32 +9819,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/{drug_id}</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>약품 상세 조회</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9844,32 +9854,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/medications</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>기록별 약품 목록 조회</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9879,32 +9889,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>LLM 복약/생활습관 가이드 생성</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9914,32 +9924,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/{guide_id}</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>가이드 상세 조회</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9949,32 +9959,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/guide</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>기록별 최신 가이드 조회</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9984,32 +9994,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>상담 세션 생성</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10019,32 +10029,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>상담 세션 목록 조회</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10054,32 +10064,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>상담 메시지 목록 조회</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="26">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10089,32 +10099,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>챗봇 메시지 전송 및 답변 생성</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="26">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10124,32 +10134,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>/api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>비동기 작업 상태 조회</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10159,32 +10169,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>/api/v1/feedbacks</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>복약 가이드 피드백 단순 등록</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10194,32 +10204,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>알림 목록 조회</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10229,32 +10239,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/unread-count</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>미읽음 알림 개수 조회</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10264,32 +10274,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}/read</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>알림 읽음 처리</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="26">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10299,17 +10309,17 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
@@ -10946,15 +10956,15 @@
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="26">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10964,32 +10974,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경 ⭐ v3</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="26">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="33" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10999,32 +11009,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회 ⭐ v3</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="26">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -11034,17 +11044,17 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents/{consent_type}</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>약관 동의 토글 (선택 약관) ⭐ v3</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
@@ -12035,84 +12045,84 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>규칙 / 정책</t>
         </is>
       </c>
     </row>
     <row r="5" ht="49.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Base URL</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>/api/v1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>인증 방식</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Bearer Token (JWT). Authorization: Bearer {access_token} 헤더로 전달.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>토큰 정책</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>access_token 유효기간 1시간, refresh_token 유효기간 14일. 5회 연속 로그인 실패 시 10분 잠금.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="49.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Content-Type</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>기본 application/json. 파일 업로드는 multipart/form-data.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="49.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>요청·응답 인코딩</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>UTF-8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="252" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>⭐ 상태코드 정책 v2</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>멘토 피드백 반영: 400으로 통일. 422 사용하지 않음. 
 • 200 OK: 조회·수정 성공
@@ -12132,12 +12142,12 @@
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>⭐ LLM 실패 처리 v2</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>멘토 피드백 반영: "500 LLM 실패" 별도 항목 사용하지 않음.
 • LLM 생성 실패 → processing_jobs.status = 'failed' + error_message 저장
@@ -12148,12 +12158,12 @@
       </c>
     </row>
     <row r="12" ht="54" customHeight="1" s="26">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>⭐ 비동기 작업 응답</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>OCR·LLM은 동기 응답 대신 202 Accepted + job_id 반환.
 클라이언트는 GET /processing-jobs/{job_id}로 상태 폴링.
@@ -12162,12 +12172,12 @@
       </c>
     </row>
     <row r="13" ht="72" customHeight="1" s="26">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>타임아웃 정책</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>• OCR Job: 60초
 • LLM Job: 90초
@@ -12177,12 +12187,12 @@
       </c>
     </row>
     <row r="14" ht="72" customHeight="1" s="26">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>⭐ 식약처 API 출처</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>공공데이터포털 - 식품의약품안전처 의약품 제품 허가 정보
 https://www.data.go.kr/data/15095677/openapi.do
@@ -12192,36 +12202,36 @@
       </c>
     </row>
     <row r="15" ht="49.5" customHeight="1" s="26">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>페이지네이션</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>조회 API는 ?page={n}&amp;size={n} 또는 ?offset={n}&amp;limit={n} 쿼리 파라미터 지원. (챗봇 상담 목록 등은 offset/limit 적용)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="49.5" customHeight="1" s="26">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>요청 검증</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>필수값 누락·타입 오류·비즈니스 검증 실패는 모두 400으로 통일. detail 필드에 사용자에게 표시 가능한 메시지 포함.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="72" customHeight="1" s="26">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>페이로드 검증 예시</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>{
   "detail": "이미 가입된 이메일입니다.",
@@ -12231,48 +12241,48 @@
       </c>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="26">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>민감정보 마스킹</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>로그·에러 응답에 OCR 원문·건강정보·토큰·API Key 노출 금지. 마스킹 또는 출력 제외 처리.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="49.5" customHeight="1" s="26">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>사용자 데이터 격리</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>모든 인증 API는 토큰의 user_id와 리소스의 user_id 검증. 타 사용자 접근 시 403 또는 404 반환.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="49.5" customHeight="1" s="26">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Rate Limit (예정)</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Sprint 3에서 도입 검토. 챗봇 메시지 등 비용 부담 API는 429 응답 + Retry-After 헤더.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="49.5" customHeight="1" s="26">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>API 버전 관리</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>URL 경로에 버전 명시 (/api/v1/...). 호환성 깨지는 변경 시 /v2/ 추가.</t>
         </is>
@@ -13300,259 +13310,259 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>작업 유형</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>트리거 API</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>상태 조회 API</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>타임아웃</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>성공 시</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>실패 시</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>OCR 처리</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/ocr/jobs</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>60초</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>status=completed → ocr_text·medications 후보 저장</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>status=failed 또는 timeout → 사용자에게 재시도 또는 직접 입력 안내</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>식약처 약품 조회</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search (동기 + 캐시)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>(N/A - 동기)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>drug_references 저장 + drug_caches 갱신</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>drug_caches 있으면 캐시 반환 + 마지막 조회 시각 표시 / 없으면 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>LLM 가이드 생성</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/guides</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>90초</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>status=completed → guides·guide_items 저장 + 알림 생성</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>status=failed → 사용자에게 재시도 안내 + 알림 생성</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>챗봇 메시지</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions/{id}/messages (동기, 5초 목표)</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>(N/A - 동기)</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>ssistant_message 즉시 응답 + safety_flag 평가</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>status=failed 응답 + 사용자에게 "답변 생성 실패" 안내</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>RAG 임베딩 (Sprint 3)</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/guideline-sources</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>120초</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>guideline_chunks + embedding_vector 저장</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>embedding_status=failed → 운영자 재시도</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>FHIR 연동 (상용화)</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/fhir/connections</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>fhir_connections.connection_status=connected</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>502 Bad Gateway + retry_count 증가</t>
         </is>
@@ -14573,447 +14583,447 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>평가요건</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>요구사항 ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>관련 API</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>산출물 위치</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4" ht="49.5" customHeight="1" s="26">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>1-1. LLM 기반 안내 가이드 생성</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>REQ-GUIDE-001/002</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>POST /guides, GET /guides/{guide_id}</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>guides·guide_items 테이블, 가이드 결과 화면</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>복약 + 생활습관 가이드 + 의료 안전 고지</t>
         </is>
       </c>
     </row>
     <row r="5" ht="49.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1-2. RAG 파이프라인 (공식협회 기반)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>REQ-RAG-PILOT-001 / REQ-RAG-001</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>POST /guideline-sources, GET /guideline-sources/search</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>guideline_sources·chunks 테이블</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 파일럿 → Sprint 3 pgvector 고도화</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2-1. 실시간 챗봇 (맥락 반영)</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>REQ-CHAT-001/002</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions, POST /chat/sessions/{id}/messages, GET /chat/sessions/{id}/messages</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>chat_sessions·messages 테이블</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>최근 3~5개 메시지 context 포함</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2-2. 챗봇 위험 질문 안전 응답</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>REQ-CHAT-003 / REQ-SAFE-001</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions/{id}/messages (safety_flag)</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>chat_messages.safety_flag</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>키워드 기반 1차 감지 + 상시 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="8" ht="49.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3-1. OCR 기반 의료정보 인식</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001/002</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /ocr/jobs, GET /processing-jobs/{job_id}, GET /records/{id}/ocr-result</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>medical_records·processing_jobs</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Upstage OCR + 라인 단위 저장</t>
         </is>
       </c>
     </row>
     <row r="9" ht="49.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>3-2. OCR 결과 사용자 검수</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-002</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>PATCH /records/{id}/ocr-text, PATCH /medications/{id}/verify</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>medications.is_verified</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>신뢰도 70% 미만 강조</t>
         </is>
       </c>
     </row>
     <row r="10" ht="49.5" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>3-3. 복약알림 (필수 MVP)</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>REQ-NOTI-001</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>GET /notifications, GET /notifications/unread-count, PATCH /notifications/{id}/read, DELETE /notifications/{id}</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>notifications 테이블</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>⭐ v2 P0 상향 (내부 알림함)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="49.5" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>3-4. 피드백 수집 (필수 MVP)</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>REQ-FB-001</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>POST /feedbacks</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>feedbacks 테이블</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>⭐ v2 P0 상향 (가이드·챗봇 피드백)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="49.5" customHeight="1" s="26">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>4-1. 사용자 데이터 접근 제어</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>REQ-SEC-001</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>전체 인증 필요 API</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>user_id 검증 미들웨어</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n"/>
+      <c r="E12" s="36" t="n"/>
     </row>
     <row r="13" ht="49.5" customHeight="1" s="26">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>4-2. 민감정보 보호·로그 마스킹</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>REQ-SEC-002</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>(전체)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>로그 정책 문서</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n"/>
+      <c r="E13" s="36" t="n"/>
     </row>
     <row r="14" ht="49.5" customHeight="1" s="26">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>5-1. API 성능 측정 (P95)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>REQ-NF-002</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>주요 조회 API</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>API 성능 테스트 문서</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>P95 3초 목표</t>
         </is>
       </c>
     </row>
     <row r="15" ht="49.5" customHeight="1" s="26">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>5-2. 비동기 처리</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>REQ-NF-001</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>POST /ocr/jobs, POST /guides, GET /processing-jobs/{id}</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>processing_jobs 테이블</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>타임아웃 관리 포함</t>
         </is>
       </c>
     </row>
     <row r="16" ht="49.5" customHeight="1" s="26">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>5-3. 식약처 API 연동</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/search, GET /drugs/{id}</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>drug_references·drug_caches·api_failure_logs</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>⭐ 공공데이터포털 링크 명시</t>
         </is>
       </c>
     </row>
     <row r="17" ht="49.5" customHeight="1" s="26">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>6-1. 핵심 플로우 (3~5단계)</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>REQ-UX-001</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>전체 화면 흐름</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>와이어프레임 #01~#18 + User Flow</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n"/>
+      <c r="E17" s="36" t="n"/>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="26">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>6-2. 협업·문서화</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>REQ-DOC-001</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>(N/A - 문서)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>R&amp;R, Git, ERD, API 명세서 v2, 와이어프레임</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Git 브랜치 전략 4개</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>3-5. 마이페이지 (계정 관리) ⭐</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 ⭐ v3</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>GET/PATCH /users/me, PATCH password, DELETE /users/me, GET /users/me/consents</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>users 테이블 + user_consents + auth_tokens</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (팀원 피드백)</t>
         </is>
@@ -16039,132 +16049,132 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>핵심 범위 (Sprint 2 MVP)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Git 브랜치</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>돈유정</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>회원가입/로그인/JWT, 사용자/건강 프로필, 의료 문서 업로드, OCR 작업 생성/조회/수정, processing_jobs 상태 조회, 알림 API (P0 상향)</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>feature/backend-auth-ocr</t>
         </is>
       </c>
     </row>
     <row r="6" ht="79.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>신정호</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Backend B (RAG 파이프라인 중심)</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>식약처 API 약품 검색·후보 선택, 챗봇 API, 위험 질문 감지, API 명세서 최신화, 공식협회 기반 RAG 흐름 연결, 피드백 등록 (P0 상향)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>feature/backend-guide-chat</t>
         </is>
       </c>
     </row>
     <row r="7" ht="79.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>조이레</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Frontend + 총괄</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>반응형 웹 화면 전체 (#01~#18), 와이어프레임 기반 UI 구현, API 연결, 알림함·피드백 UI</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>feature/frontend-responsive-web</t>
         </is>
       </c>
     </row>
     <row r="8" ht="79.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>이정훈</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>AI/Infra + 배포</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>OCR API 테스트/구현, LLM 프롬프트 작성, 복약/생활습관 가이드 생성, 챗봇 안전 응답 프롬프트, 위험 질문 키워드, 공통 에러/테스트 케이스, 배포</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>feature/ai-prompt-test</t>
         </is>
       </c>
     </row>
     <row r="9" ht="79.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>유태영</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>멘토</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>기획 리뷰·피드백·평가 항목 점검</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>(N/A)</t>
         </is>
@@ -17192,459 +17202,459 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>상태코드 정책</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>400 / 422 입력값 검증 실패 구분</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>400으로 통일 (모든 입력 오류 포함)</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>멘토: 토스 개발자 센터 참고</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>LLM 실패 처리</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>POST /chat/messages → 500 LLM 실패</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>※ LLM 실패는 job status=failed로 처리 (HTTP 상태가 아닌 비즈니스 상태)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>멘토: 500 LLM 실패 항목 삭제</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>POST /records 응답</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>500 저장 실패 포함</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>500 저장 실패 제거 (서버 내부 오류로 일반화)</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>상태코드 정리</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>/api/v1/admin/operation-logs</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>P3 상용화 검토에 포함</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>API 명세에서 완전 삭제</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>멘토: 운영 로그는 ERD 내부 검토만</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/notifications</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Sprint 3 P2</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>멘토: 복약알림 필수 MVP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/feedbacks</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 Stretch P1</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>멘토: 피드백 필수 MVP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/notifications/unread-count</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>대시보드 알림 뱃지 (멘토: 알림 디테일)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>PATCH /api/v1/notifications/{id}/read</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>내부 알림함 (멘토 피드백)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>DELETE /api/v1/notifications/{id}</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>내부 알림함 (멘토 피드백)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search 비고</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>"식약처 API 호출"</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>+ 공공데이터포털 URL 추가</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>멘토: 식약처 API 데이터셋 링크</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/{drug_id} 비고</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>기본 설명</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>+ 제조사 정보 포함 응답 명시</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>멘토: 제조사 다른 경우 표시</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>/api/v1/challenge-checkins</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Sprint 3 P2</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>확인 완료 — Sprint 3 P2 유지</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>멘토: 확인 요청 답변</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>공통 규칙 시트</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>기본 규칙만</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>+ 상태코드 정책, LLM 실패 처리, 식약처 출처 추가</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>v2 전체 정책 통일</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>20개 시트</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>8개 시트로 통합</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>도메인별 분리 시트들을 우선순위로 통합</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Sprint 우선순위 분류</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Sprint2_MVP_P0, Sprint2_Stretch_P1, Sprint3_P2, Commercial_P3 4개 시트</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>1개 시트로 통합 (단계 컬럼 필터)</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>도메인별 시트</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>회원_사용자, 기록_OCR, 약품_가이드, 챗봇_작업상태, Sprint3_확장, 상용화_검토 6개 시트</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>전체 명세 시트의 도메인 컬럼으로 대체</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
@@ -17659,270 +17669,270 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Before (v2)</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>After (v3)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>POST /auth/login 비고</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>+ 통합 메시지 응답 명시 (계정 존재 노출 방지)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>REQ-AUTH-002 (팀원 보안 피드백)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="26">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>GET /records/{id}/ocr 비고</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>+ medications[].manufacturer 필수 명시</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="26">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/search 비고</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>식약처 API 호출</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>+ manufacturer 필수 필드 ("제조사 정보 없음" 폴백)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/{id} 비고</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>+ manufacturer 필수 필드 명시</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>POST /records 비고</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>image_expires_at 90일 보존</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>+ REQ-REC-001과 일치 확인 완료 추가</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>팀원 피드백: 요구사항·API 일치 확인</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>전체 API 수</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>47개</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>49개 (+2 마이페이지)</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 신규</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0 API 수</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>29개</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>31개 (+2 마이페이지)</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>마이페이지 P0</t>
         </is>
@@ -17937,216 +17947,216 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="26">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="26">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 상세 요구사항</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>7개 메뉴 간단 나열</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>10개 메뉴 + 비밀번호 변경 4단계 + 회원탈퇴 5단계 + 약관 5개 관리 상세</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>팀원: 마이페이지 자세히 작성</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="26">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password 비고</t>
         </is>
       </c>
-      <c r="C37" s="25" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>+ 4단계 흐름, 5회 실패 10분 제한, 이메일·이름·닉네임 동일 제한</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>비밀번호 변경 상세화</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="26">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>DELETE /users/me 비고</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>+ 5단계 흐름, 5회 실패 24시간 제한, OCR/LLM cancelled, 30일 영구 삭제 배치</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>회원탈퇴 상세화</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="26">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents 비고</t>
         </is>
       </c>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>+ 5개 약관 (terms/privacy/health_data/ai_analysis/marketing), 전문 보기</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>약관 관리 상세화</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="26">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me 비고</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>+ 30일 1회 변경 제한, 욕설 필터링, 다음 변경 가능일 메시지</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>닉네임 정책 명시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="26">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/consents/{type}</t>
         </is>
       </c>
-      <c r="C41" s="25" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>신규 추가 (선택 약관 토글, 필수 약관은 400)</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="36" t="inlineStr">
         <is>
           <t>마케팅 수신 토글용</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="26">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t>전체 API 개수</t>
         </is>
       </c>
-      <c r="C42" s="25" t="inlineStr">
+      <c r="C42" s="36" t="inlineStr">
         <is>
           <t>49개</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>50개 (+1)</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
         <is>
           <t>약관 토글 추가</t>
         </is>

--- a/docs/api/api-spec-final.xlsx
+++ b/docs/api/api-spec-final.xlsx
@@ -7365,13 +7365,13 @@
       <c r="P55" s="33" t="inlineStr">
         <is>
           <t>{
-  "detail": "인증 코드가 발송되었습니다."
+  "detail": "인증 코드가 이메일로 발송되었습니다."
 }</t>
         </is>
       </c>
       <c r="Q55" s="33" t="inlineStr">
         <is>
-          <t>200 OK / 400 이메일 형식 오류 / 429 발송 쿨다운</t>
+          <t>200 OK / 400 이메일 형식 오류 / 429 발송 쿨다운 (body: {detail, retry_after})</t>
         </is>
       </c>
       <c r="R55" s="33" t="inlineStr">
@@ -7466,7 +7466,7 @@
       <c r="P56" s="33" t="inlineStr">
         <is>
           <t>{
-  "verified": true
+  "detail": "이메일 인증이 완료되었습니다."
 }</t>
         </is>
       </c>
@@ -7964,10 +7964,10 @@
       <c r="P61" s="33" t="inlineStr">
         <is>
           <t>{
-  "medication_alarm": true,
-  "challenge_alarm": true,
   "guide_complete_alarm": true,
-  "push_permission": true
+  "ocr_complete_alarm": true,
+  "system_alarm": true,
+  "updated_at": "2026-06-04T10:00:00Z"
 }</t>
         </is>
       </c>
@@ -8269,14 +8269,12 @@
       <c r="O64" s="33" t="n"/>
       <c r="P64" s="33" t="inlineStr">
         <is>
-          <t>{
-  "detail": "삭제되었습니다."
-}</t>
+          <t>204 No Content (응답 본문 없음)</t>
         </is>
       </c>
       <c r="Q64" s="33" t="inlineStr">
         <is>
-          <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
+          <t>204 No Content / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
       <c r="R64" s="33" t="inlineStr">

--- a/docs/api/api-spec-final.xlsx
+++ b/docs/api/api-spec-final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. v3 팀원 피드백 API 수정" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 전체 API 명세 v3" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Sprint 우선순위 분류" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 공통 규칙 v2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 비동기 처리 흐름" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 평가요건 매핑" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 담당자 역할 기준" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 변경 이력" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="0. v3 팀원 피드백 API 수정" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. 전체 API 명세 v3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Sprint 우선순위 분류" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. 공통 규칙 v2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. 비동기 처리 흐름" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. 평가요건 매핑" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. 담당자 역할 기준" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. 변경 이력" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,119 +575,119 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>팀원 피드백</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>API 변경 내역</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 마이페이지 요구사항 신규 추가</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>PATCH /api/v1/users/me/password 신규 추가 (P0)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/users/me/consents 신규 추가 (P0)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>REQ-AUTH-002 로그인 메시지 보안 강화</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/auth/login Error Response 비고 업데이트</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>REQ-REC-001 이미지 보관 90일 확정</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/records 비고는 이미 90일로 명시 (변경 불필요)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001 약품 카드 제조사 포함</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/records/{record_id}/ocr 응답 스키마에 manufacturer 명시</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 제조사 무조건 표기</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search, /drugs/{id} 응답 스키마에 manufacturer 필수 명시</t>
         </is>
@@ -701,81 +701,81 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>관련 요구사항</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 / P0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 / P0</t>
         </is>
@@ -789,102 +789,102 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>v3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>전체 API 개수</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>47개</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>49개 (+2)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0 API</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>29개</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>31개 (+2 마이페이지)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>마이페이지 도메인</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>GET/PATCH/DELETE /users/me (3개)</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>+ PATCH password + GET consents (5개)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>로그인 보안</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>구분 메시지</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>통합 메시지 (계정 존재 노출 방지)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>약품 응답</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>제조사 선택적</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>manufacturer 필수 필드 명시</t>
         </is>
@@ -899,119 +899,119 @@
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>변경 내용</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>관련 API</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 — 메뉴 10개·비밀번호 변경 4단계·회원탈퇴 5단계 상세 명시</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>(요구사항 정의서 본문)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>비밀번호 변경 API 비고 보강 (4단계 흐름, 5회 실패 10분 제한, 모든 기기 로그아웃)</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>회원탈퇴 API 비고 보강 (5단계 흐름, 5회 실패 24시간 제한, OCR/LLM cancelled, 30일 영구 삭제)</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>DELETE /users/me</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="26">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>약관 동의 조회 API 비고 보강 (5개 약관 + 전문 보기 링크)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="26">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>닉네임 수정 API 비고 보강 (30일 1회 제한, 욕설 필터링)</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="26">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>선택 약관 토글 API 신규 추가 (마케팅 수신 동의/철회)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/consents/{consent_type} ⭐ 신규</t>
         </is>
@@ -2034,132 +2034,132 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" s="26">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>기능 단계</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>도메인</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>API명</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>Request URL</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>HTTP Method</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>인증 필요</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>비동기 여부</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="35" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t>Header Schema</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="35" t="inlineStr">
         <is>
           <t>Query Parameter Schema</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="35" t="inlineStr">
         <is>
           <t>Request Body Example</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="35" t="inlineStr">
         <is>
           <t>Success Response Example</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="35" t="inlineStr">
         <is>
           <t>Error Response / Status Code</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R4" s="35" t="inlineStr">
         <is>
           <t>관련 ERD 테이블</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="35" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="35" t="inlineStr">
         <is>
           <t>완료 상태</t>
         </is>
       </c>
     </row>
     <row r="5" ht="127.5" customHeight="1" s="26">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>회원가입 및 필수 동의 저장</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/signup</t>
         </is>
@@ -2169,38 +2169,38 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>이메일 회원가입과 필수 약관/민감정보/AI 분석 동의를 한 번에 저장한다.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t>Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t>{
   "email": "user@example.com",
@@ -2228,7 +2228,7 @@
 }</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t>{
   "user_id": 1,
@@ -2237,52 +2237,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 필수값 누락 / 409 이메일 중복</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="33" t="inlineStr">
         <is>
           <t>users, user_consents</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t>이메일 형식, 비밀번호 정책 검증 포함</t>
         </is>
       </c>
-      <c r="T5" s="27" t="inlineStr">
+      <c r="T5" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>로그인 및 토큰 발급</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/login</t>
         </is>
@@ -2292,38 +2292,38 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>로그인 성공 시 access_token과 refresh_token을 발급한다.</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="33" t="inlineStr">
         <is>
           <t>Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t>{
   "email": "user@example.com",
@@ -2331,7 +2331,7 @@
 }</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t>{
   "access_token": "jwt.access",
@@ -2344,7 +2344,7 @@
 }</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 입력 오류
@@ -2352,47 +2352,47 @@
 429 5회 연속 실패 잠금</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr">
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>users, auth_tokens</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="S6" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 팀원 피드백: 개인정보 보안 — 401 응답 시 계정 없음/비밀번호 불일치 구분 없이 통합 메시지</t>
         </is>
       </c>
-      <c r="T6" s="27" t="inlineStr">
+      <c r="T6" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/logout</t>
         </is>
@@ -2402,93 +2402,93 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>현재 refresh token을 revoke 처리한다.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="N7" s="33" t="n"/>
+      <c r="O7" s="33" t="inlineStr">
         <is>
           <t>{
   "refresh_token": "jwt.refresh"
 }</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "로그아웃되었습니다."
 }</t>
         </is>
       </c>
-      <c r="Q7" s="11" t="inlineStr">
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R7" s="11" t="inlineStr">
+      <c r="R7" s="33" t="inlineStr">
         <is>
           <t>auth_tokens</t>
         </is>
       </c>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="27" t="inlineStr">
+      <c r="S7" s="33" t="n"/>
+      <c r="T7" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>내 정보 조회</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me</t>
         </is>
@@ -2498,39 +2498,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>로그인한 사용자의 기본 정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L8" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="N8" s="33" t="n"/>
+      <c r="O8" s="33" t="n"/>
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t>{
   "user_id": 1,
@@ -2541,48 +2541,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q8" s="11" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R8" s="11" t="inlineStr">
+      <c r="R8" s="33" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="27" t="inlineStr">
+      <c r="S8" s="33" t="n"/>
+      <c r="T8" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="9" ht="63.75" customHeight="1" s="26">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>건강정보</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 저장/수정</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
@@ -2592,39 +2592,39 @@
           <t>PUT</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드와 챗봇 context에 사용할 최소 건강정보를 저장한다.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="L9" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="N9" s="33" t="n"/>
+      <c r="O9" s="33" t="inlineStr">
         <is>
           <t>{
   "age_group": "30s",
@@ -2643,7 +2643,7 @@
 }</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P9" s="33" t="inlineStr">
         <is>
           <t>{
   "profile_id": 1,
@@ -2651,48 +2651,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 잘못된 입력 / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R9" s="11" t="inlineStr">
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>user_health_profiles</t>
         </is>
       </c>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="27" t="inlineStr">
+      <c r="S9" s="33" t="n"/>
+      <c r="T9" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="26">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>건강정보</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 조회</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
@@ -2702,39 +2702,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>현재 로그인 사용자의 건강정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="N10" s="33" t="n"/>
+      <c r="O10" s="33" t="n"/>
+      <c r="P10" s="33" t="inlineStr">
         <is>
           <t>{
   "profile_id": 1,
@@ -2750,48 +2750,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="inlineStr">
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 404 프로필 없음</t>
         </is>
       </c>
-      <c r="R10" s="11" t="inlineStr">
+      <c r="R10" s="33" t="inlineStr">
         <is>
           <t>user_health_profiles</t>
         </is>
       </c>
-      <c r="S10" s="11" t="n"/>
-      <c r="T10" s="27" t="inlineStr">
+      <c r="S10" s="33" t="n"/>
+      <c r="T10" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="26">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>의료 이미지 업로드</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
@@ -2801,45 +2801,45 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>처방전/약봉투/진료기록 이미지 또는 PDF를 업로드하고 record_id를 생성한다.</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="L11" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: multipart/form-data</t>
         </is>
       </c>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="N11" s="33" t="n"/>
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t>file: binary
 record_type: prescription|medicine_bag|medical_record</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -2850,52 +2850,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">201 Created / 400 파일 형식 오류 / 401 인증 실패 / 413 용량 초과 </t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
+      <c r="R11" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="33" t="inlineStr">
         <is>
           <t>image_expires_at 90일 보존 정책 반영 | ⭐ v3: 요구사항 REQ-REC-001과 90일 정책 일치 확인 완료 (팀원 피드백)</t>
         </is>
       </c>
-      <c r="T11" s="27" t="inlineStr">
+      <c r="T11" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1" s="26">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>진료기록 목록 조회</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
@@ -2905,43 +2905,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>사용자의 업로드 기록 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="33" t="inlineStr">
         <is>
           <t>page, size, record_type</t>
         </is>
       </c>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="O12" s="33" t="n"/>
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -2957,48 +2957,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="Q12" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R12" s="11" t="inlineStr">
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="27" t="inlineStr">
+      <c r="S12" s="33" t="n"/>
+      <c r="T12" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" s="26">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>진료기록 상세 조회</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}</t>
         </is>
@@ -3008,90 +3008,100 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>record_id 기준으로 업로드 정보와 처리 상태를 조회한다.</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K13" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L13" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="N13" s="33" t="n"/>
+      <c r="O13" s="33" t="n"/>
+      <c r="P13" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
   "record_type": "prescription",
   "status": "ocr_completed",
-  "ocr_confidence": 0.91
+  "file_url": "https://.../rx.png",
+  "file_name": "처방전.png",
+  "file_size": 123456,
+  "content_type": "image/png",
+  "ocr_text": "...",
+  "ocr_edited_text": null,
+  "ocr_confidence": 0.91,
+  "input_method": "upload",
+  "image_expires_at": "2026-09-01T00:00:00Z",
+  "uploaded_at": "2026-06-04T10:00:00Z",
+  "updated_at": "2026-06-04T10:05:00Z"
 }</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="inlineStr">
+      <c r="Q13" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 타 사용자 기록 접근 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R13" s="11" t="inlineStr">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="27" t="inlineStr">
+      <c r="S13" s="33" t="n"/>
+      <c r="T13" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" s="26">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>OCR 작업 시작</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>/api/v1/ocr/jobs</t>
         </is>
@@ -3101,39 +3111,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>업로드된 record_id에 대해 OCR 비동기 작업을 시작하고 job_id를 반환한다.</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="N14" s="33" t="n"/>
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3141,7 +3151,7 @@
 }</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P14" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 101,
@@ -3151,52 +3161,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t>202 Accepted / 400 잘못된 record_id / 401 인증 실패 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R14" s="11" t="inlineStr">
+      <c r="R14" s="33" t="inlineStr">
         <is>
           <t>processing_jobs, medical_records</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="S14" s="33" t="inlineStr">
         <is>
           <t>P95 3초 대응을 위해 job_id 반환 방식</t>
         </is>
       </c>
-      <c r="T14" s="27" t="inlineStr">
+      <c r="T14" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="26">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 조회</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-result</t>
         </is>
@@ -3206,39 +3216,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>OCR 원문, 편집본, 신뢰도, 약품 후보를 조회한다.</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L15" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="N15" s="33" t="n"/>
+      <c r="O15" s="33" t="n"/>
+      <c r="P15" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3255,52 +3265,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 타 사용자 기록 접근 / 404 결과 없음</t>
         </is>
       </c>
-      <c r="R15" s="11" t="inlineStr">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>medical_records, medications</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="S15" s="33" t="inlineStr">
         <is>
           <t>⭐ v3: 응답에 medications[].manufacturer 필수 포함 (팀원 피드백)</t>
         </is>
       </c>
-      <c r="T15" s="27" t="inlineStr">
+      <c r="T15" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="26">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 수정</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-text</t>
         </is>
@@ -3310,46 +3320,46 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>사용자가 OCR 결과를 확인/수정하고 저장한다.</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="N16" s="33" t="n"/>
+      <c r="O16" s="33" t="inlineStr">
         <is>
           <t>{
   "ocr_edited_text": "타이레놀 500mg 1정 식후 복용"
 }</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P16" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3358,48 +3368,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="Q16" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 입력값 오류 / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R16" s="11" t="inlineStr">
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="27" t="inlineStr">
+      <c r="S16" s="33" t="n"/>
+      <c r="T16" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1" s="26">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>OCR 약품명 확인</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/medications/{medication_id}/verify</t>
         </is>
@@ -3409,39 +3419,39 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>OCR 신뢰도 낮은 약품명을 사용자가 확인하고 is_verified를 true로 저장한다.</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K17" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L17" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="N17" s="33" t="n"/>
+      <c r="O17" s="33" t="inlineStr">
         <is>
           <t>{
   "drug_name": "타이레놀정500mg",
@@ -3449,7 +3459,7 @@
 }</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P17" s="33" t="inlineStr">
         <is>
           <t>{
   "medication_id": 30,
@@ -3458,52 +3468,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="inlineStr">
+      <c r="Q17" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 입력 오류 / 401 인증 실패 / 404 약품 없음</t>
         </is>
       </c>
-      <c r="R17" s="11" t="inlineStr">
+      <c r="R17" s="33" t="inlineStr">
         <is>
           <t>medications</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="33" t="inlineStr">
         <is>
           <t>신뢰도 기준 미만 후보를 사용자 확인 대상으로 표시</t>
         </is>
       </c>
-      <c r="T17" s="27" t="inlineStr">
+      <c r="T17" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1" s="26">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>식약처 약품 검색</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/search</t>
         </is>
@@ -3513,43 +3523,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>약품명, 일반명, 성분명 기준으로 식약처 API 또는 캐시에서 약품을 검색한다.</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>부분 비동기</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="L18" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N18" s="33" t="inlineStr">
         <is>
           <t>q, search_type, page, size</t>
         </is>
       </c>
-      <c r="O18" s="11" t="n"/>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="O18" s="33" t="n"/>
+      <c r="P18" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -3563,52 +3573,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q18" s="11" t="inlineStr">
+      <c r="Q18" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 검색어 누락 / 401 인증 실패 / 504 외부 API timeout</t>
         </is>
       </c>
-      <c r="R18" s="11" t="inlineStr">
+      <c r="R18" s="33" t="inlineStr">
         <is>
           <t>drug_references, drug_caches, api_failure_logs</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="33" t="inlineStr">
         <is>
           <t>⭐ 식약처 의약품안전나라 (공공데이터포털): https://www.data.go.kr/data/15095677/openapi.do | 일반명↔상품명 양방향 검색, 캐시 7일 | ⭐ v3: 응답 스키마에 manufacturer 필수 필드 (누락 시 "제조사 정보 없음")</t>
         </is>
       </c>
-      <c r="T18" s="27" t="inlineStr">
+      <c r="T18" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1" s="26">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>약품 상세 조회</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/{drug_id}</t>
         </is>
@@ -3618,39 +3628,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>식약처 기준 약품 상세 정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="N19" s="33" t="n"/>
+      <c r="O19" s="33" t="n"/>
+      <c r="P19" s="33" t="inlineStr">
         <is>
           <t>{
   "drug_ref_id": 100,
@@ -3662,52 +3672,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="inlineStr">
+      <c r="Q19" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 404 약품 없음</t>
         </is>
       </c>
-      <c r="R19" s="11" t="inlineStr">
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>drug_references</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="S19" s="33" t="inlineStr">
         <is>
           <t>⭐ 식약처 의약품 제품 허가정보. 제조사 정보 포함 응답 | ⭐ v3: manufacturer 필수 필드 명시</t>
         </is>
       </c>
-      <c r="T19" s="27" t="inlineStr">
+      <c r="T19" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1" s="26">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>기록별 약품 목록 조회</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/medications</t>
         </is>
@@ -3717,39 +3727,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>OCR 또는 직접 입력으로 추출/저장된 약품 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L20" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="M20" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="11" t="n"/>
-      <c r="P20" s="11" t="inlineStr">
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3765,52 +3775,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q20" s="11" t="inlineStr">
+      <c r="Q20" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R20" s="11" t="inlineStr">
+      <c r="R20" s="33" t="inlineStr">
         <is>
           <t>medications</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>⭐ v4: 미구현 — ocr-result의 medication_candidates로 대체 추정 (확인 필요)</t>
+      <c r="S20" s="33" t="inlineStr">
+        <is>
+          <t>구현 완료 (Backend B). 응답 {record_id, medications:[{medication_id, drug_name, dosage, frequency, timing, duration, is_verified, ...}]}</t>
         </is>
       </c>
       <c r="T20" s="28" t="inlineStr">
         <is>
-          <t>미구현 (확인필요)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1" s="26">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>LLM 복약/생활습관 가이드 생성</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/generate</t>
         </is>
@@ -3820,39 +3830,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="33" t="inlineStr">
         <is>
           <t>OCR 수정본, 약품 정보, 건강정보를 context로 LLM 가이드 생성 작업을 시작한다.</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L21" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M21" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="N21" s="33" t="n"/>
+      <c r="O21" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3860,7 +3870,7 @@
 }</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P21" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 201,
@@ -3869,53 +3879,53 @@
 }</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="inlineStr">
+      <c r="Q21" s="33" t="inlineStr">
         <is>
           <t>202 Accepted / 400 입력 오류 / 401 인증 실패 / 404 record 없음 / 504 LLM timeout</t>
         </is>
       </c>
-      <c r="R21" s="11" t="inlineStr">
+      <c r="R21" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items, processing_jobs</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="S21" s="33" t="inlineStr">
         <is>
           <t>model_name, prompt_version 저장
 ⭐ v4: 실제 경로 /guides → /guides/generate 반영</t>
         </is>
       </c>
-      <c r="T21" s="27" t="inlineStr">
+      <c r="T21" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="22" ht="63.75" customHeight="1" s="26">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>가이드 상세 조회</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/{guide_id}</t>
         </is>
@@ -3925,39 +3935,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>생성된 복약/생활습관 가이드와 항목별 guide_items를 조회한다.</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="11" t="n"/>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="33" t="inlineStr">
         <is>
           <t>{
   "guide_id": 50,
@@ -3977,48 +3987,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q22" s="11" t="inlineStr">
+      <c r="Q22" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 가이드 없음</t>
         </is>
       </c>
-      <c r="R22" s="11" t="inlineStr">
+      <c r="R22" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items</t>
         </is>
       </c>
-      <c r="S22" s="11" t="n"/>
-      <c r="T22" s="27" t="inlineStr">
+      <c r="S22" s="33" t="n"/>
+      <c r="T22" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1" s="26">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>기록별 최신 가이드 조회</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/guide</t>
         </is>
@@ -4028,39 +4038,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>record_id 기준 최신 가이드 결과를 조회한다.</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="L23" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="N23" s="33" t="n"/>
+      <c r="O23" s="33" t="n"/>
+      <c r="P23" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -4070,52 +4080,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="inlineStr">
+      <c r="Q23" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 가이드 없음</t>
         </is>
       </c>
-      <c r="R23" s="11" t="inlineStr">
+      <c r="R23" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items</t>
         </is>
       </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>⭐ v4: 미구현 — GET /guides/{guide_id}로 대체 (확인 필요)</t>
+      <c r="S23" s="33" t="inlineStr">
+        <is>
+          <t>구현 완료 (#104, Backend B). 응답은 GET /guides/{guide_id}와 동일 (GenerateGuideResponse)</t>
         </is>
       </c>
       <c r="T23" s="28" t="inlineStr">
         <is>
-          <t>미구현 (확인필요)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
     <row r="24" ht="60" customHeight="1" s="26">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>상담 세션 생성</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
@@ -4125,39 +4135,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>record_id 또는 guide_id와 연결된 상담 세션을 생성한다.</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L24" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="11" t="inlineStr">
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -4166,7 +4176,7 @@
 }</t>
         </is>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P24" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4175,48 +4185,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q24" s="11" t="inlineStr">
+      <c r="Q24" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 입력 오류 / 401 인증 실패 / 403 권한 없음</t>
         </is>
       </c>
-      <c r="R24" s="11" t="inlineStr">
+      <c r="R24" s="33" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="27" t="inlineStr">
+      <c r="S24" s="33" t="n"/>
+      <c r="T24" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1" s="26">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>상담 세션 목록 조회</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
@@ -4226,43 +4236,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="33" t="inlineStr">
         <is>
           <t>로그인 사용자의 상담 세션 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L25" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="M25" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N25" s="33" t="inlineStr">
         <is>
           <t>offset, limit</t>
         </is>
       </c>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="inlineStr">
+      <c r="O25" s="33" t="n"/>
+      <c r="P25" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -4291,48 +4301,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="inlineStr">
+      <c r="Q25" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R25" s="11" t="inlineStr">
+      <c r="R25" s="33" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="27" t="inlineStr">
+      <c r="S25" s="33" t="n"/>
+      <c r="T25" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="26" ht="63.75" customHeight="1" s="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>상담 메시지 목록 조회</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
@@ -4342,43 +4352,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="33" t="inlineStr">
         <is>
           <t>특정 상담 세션의 메시지를 시간순으로 조회한다.</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="L26" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="M26" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N26" s="11" t="inlineStr">
+      <c r="N26" s="33" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="O26" s="11" t="n"/>
-      <c r="P26" s="11" t="inlineStr">
+      <c r="O26" s="33" t="n"/>
+      <c r="P26" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4406,48 +4416,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q26" s="11" t="inlineStr">
+      <c r="Q26" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 세션 없음</t>
         </is>
       </c>
-      <c r="R26" s="11" t="inlineStr">
+      <c r="R26" s="33" t="inlineStr">
         <is>
           <t>chat_sessions, chat_messages</t>
         </is>
       </c>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="27" t="inlineStr">
+      <c r="S26" s="33" t="n"/>
+      <c r="T26" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="27" ht="63.75" customHeight="1" s="26">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>챗봇 메시지 전송 및 답변 생성</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
@@ -4457,39 +4467,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>사용자 질문을 저장하고 최근 3~5개 메시지를 context로 LLM 또는 규칙 기반 답변을 생성한다.</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L27" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M27" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="N27" s="33" t="n"/>
+      <c r="O27" s="33" t="inlineStr">
         <is>
           <t>{
   "message": "이 약을 식후에 먹어도 되나요?",
@@ -4498,7 +4508,7 @@
 }</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P27" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4509,52 +4519,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="Q27" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 질문 누락 / 401 인증 실패 / 403 권한 없음 / 429 요청 횟수 초과 / ※ LLM 실패는 job status=failed로 처리</t>
         </is>
       </c>
-      <c r="R27" s="11" t="inlineStr">
+      <c r="R27" s="33" t="inlineStr">
         <is>
           <t>chat_messages, chat_sessions</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="S27" s="33" t="inlineStr">
         <is>
           <t>위험 질문은 safety_flag=true 및 의료기관 상담 권고</t>
         </is>
       </c>
-      <c r="T27" s="27" t="inlineStr">
+      <c r="T27" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1" s="26">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>작업 상태</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>비동기 작업 상태 조회</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>/api/v1/processing-jobs/{job_id}</t>
         </is>
@@ -4564,39 +4574,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>OCR, 약품 조회, 가이드 생성 등 비동기 작업 상태를 조회한다.</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L28" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M28" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="N28" s="33" t="n"/>
+      <c r="O28" s="33" t="n"/>
+      <c r="P28" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 101,
@@ -4609,48 +4619,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="inlineStr">
+      <c r="Q28" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 job 없음</t>
         </is>
       </c>
-      <c r="R28" s="11" t="inlineStr">
+      <c r="R28" s="33" t="inlineStr">
         <is>
           <t>processing_jobs</t>
         </is>
       </c>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="27" t="inlineStr">
+      <c r="S28" s="33" t="n"/>
+      <c r="T28" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1" s="26">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>복약 가이드 피드백 단순 등록</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>/api/v1/feedbacks</t>
         </is>
@@ -4660,39 +4670,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="33" t="inlineStr">
         <is>
           <t>가이드 또는 챗봇 답변에 대한 별점/코멘트를 등록한다.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M29" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="N29" s="33" t="n"/>
+      <c r="O29" s="33" t="inlineStr">
         <is>
           <t>{
   "guide_id": 50,
@@ -4703,7 +4713,7 @@
 }</t>
         </is>
       </c>
-      <c r="P29" s="11" t="inlineStr">
+      <c r="P29" s="33" t="inlineStr">
         <is>
           <t>{
   "feedback_id": 300,
@@ -4711,17 +4721,17 @@
 }</t>
         </is>
       </c>
-      <c r="Q29" s="11" t="inlineStr">
+      <c r="Q29" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 입력 오류 / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R29" s="11" t="inlineStr">
+      <c r="R29" s="33" t="inlineStr">
         <is>
           <t>feedbacks</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr">
+      <c r="S29" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 멘토 반영: P1 → P0 상향 (가이드·챗봇 피드백 등록 필수 MVP)
 ⭐ v4: 미구현(미착수) — 구현 여부 확인 필요</t>
@@ -4734,30 +4744,30 @@
       </c>
     </row>
     <row r="30" ht="60" customHeight="1" s="26">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>알림 목록 조회</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications</t>
         </is>
@@ -4767,43 +4777,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>사용자 알림 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="L30" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="M30" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr">
+      <c r="N30" s="33" t="inlineStr">
         <is>
           <t>page, size, is_read</t>
         </is>
       </c>
-      <c r="O30" s="11" t="n"/>
-      <c r="P30" s="11" t="inlineStr">
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -4816,52 +4826,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q30" s="11" t="inlineStr">
+      <c r="Q30" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R30" s="11" t="inlineStr">
+      <c r="R30" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="S30" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 멘토 반영: P2 → P0 상향 (내부 알림함 필수 MVP)</t>
         </is>
       </c>
-      <c r="T30" s="27" t="inlineStr">
+      <c r="T30" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1" s="26">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>미읽음 알림 개수 조회</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/unread-count</t>
         </is>
@@ -4871,91 +4881,91 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>대시보드 알림 아이콘 뱃지에 표시할 미읽음 알림 개수를 반환한다.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="L31" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="M31" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="N31" s="33" t="n"/>
+      <c r="O31" s="33" t="n"/>
+      <c r="P31" s="33" t="inlineStr">
         <is>
           <t>{
   "unread_count": 5
 }</t>
         </is>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
+      <c r="Q31" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R31" s="11" t="inlineStr">
+      <c r="R31" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="S31" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백): 대시보드 미읽음 뱃지용</t>
         </is>
       </c>
-      <c r="T31" s="27" t="inlineStr">
+      <c r="T31" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1" s="26">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>알림 읽음 처리</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}/read</t>
         </is>
@@ -4965,39 +4975,39 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>사용자가 알림을 클릭하거나 모두 읽음 처리할 때 read 상태로 변경한다.</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L32" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="M32" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-      <c r="P32" s="11" t="inlineStr">
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="33" t="inlineStr">
         <is>
           <t>{
   "notification_id": 12,
@@ -5006,52 +5016,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q32" s="11" t="inlineStr">
+      <c r="Q32" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 알림 없음</t>
         </is>
       </c>
-      <c r="R32" s="11" t="inlineStr">
+      <c r="R32" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="S32" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백)</t>
         </is>
       </c>
-      <c r="T32" s="27" t="inlineStr">
+      <c r="T32" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1" s="26">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}</t>
         </is>
@@ -5061,61 +5071,61 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="33" t="inlineStr">
         <is>
           <t>사용자가 개별 알림을 삭제한다.</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J33" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="L33" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr">
+      <c r="M33" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="11" t="inlineStr">
+      <c r="N33" s="33" t="n"/>
+      <c r="O33" s="33" t="n"/>
+      <c r="P33" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "삭제되었습니다."
 }</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="Q33" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 알림 없음</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
+      <c r="R33" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백)</t>
         </is>
       </c>
-      <c r="T33" s="27" t="inlineStr">
+      <c r="T33" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -6941,30 +6951,30 @@
       </c>
     </row>
     <row r="52" ht="180" customHeight="1" s="26">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
@@ -6974,38 +6984,38 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="33" t="inlineStr">
         <is>
           <t>사용자가 마이페이지에서 비밀번호를 변경한다. 현재 비밀번호 확인 후 새 비밀번호로 변경. 변경 성공 시 모든 기기에서 로그아웃 처리.</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="K52" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="L52" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr">
+      <c r="M52" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N52" s="11" t="n"/>
-      <c r="O52" s="11" t="inlineStr">
+      <c r="N52" s="33" t="n"/>
+      <c r="O52" s="33" t="inlineStr">
         <is>
           <t>{
   "current_password": "OldP@ssw0rd1",
@@ -7013,7 +7023,7 @@
 }</t>
         </is>
       </c>
-      <c r="P52" s="11" t="inlineStr">
+      <c r="P52" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "비밀번호가 변경되었습니다. 다시 로그인해주세요.",
@@ -7021,54 +7031,54 @@
 }</t>
         </is>
       </c>
-      <c r="Q52" s="11" t="inlineStr">
+      <c r="Q52" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 입력 오류 (정책 미충족, 현재 비밀번호와 동일)
 401 현재 비밀번호 불일치</t>
         </is>
       </c>
-      <c r="R52" s="11" t="inlineStr">
+      <c r="R52" s="33" t="inlineStr">
         <is>
           <t>users, auth_tokens</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001). 정책: 8자 이상 20자 이하, 영문 대소문자/숫자/특수문자 중 3종류 이상. ⭐ v3 업데이트: 4단계 흐름 (현재 비밀번호 → 새 비밀번호 → 확인 → 완료). 현재 비밀번호 5회 실패 시 10분 제한. 이메일·이름·닉네임과 동일하면 변경 제한. 변경 성공 시 모든 refresh_token revoke (전체 기기 강제 로그아웃)</t>
         </is>
       </c>
-      <c r="T52" s="27" t="inlineStr">
+      <c r="T52" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="53" ht="180" customHeight="1" s="26">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="33" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D53" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
@@ -7078,39 +7088,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="33" t="inlineStr">
         <is>
           <t>사용자가 가입 시 동의한 약관·개인정보 처리방침·민감 건강정보 수집·AI 분석 활용·마케팅 등 동의 내역을 조회한다.</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I53" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J53" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="K53" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L53" s="11" t="inlineStr">
+      <c r="L53" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="M53" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="inlineStr">
+      <c r="N53" s="33" t="n"/>
+      <c r="O53" s="33" t="n"/>
+      <c r="P53" s="33" t="inlineStr">
         <is>
           <t>{
   "consents": [
@@ -7148,53 +7158,53 @@
 }</t>
         </is>
       </c>
-      <c r="Q53" s="11" t="inlineStr">
+      <c r="Q53" s="33" t="inlineStr">
         <is>
           <t>200 OK
 401 인증 실패</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr">
+      <c r="R53" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr">
+      <c r="S53" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001). 마이페이지 &gt; 약관 동의 내역 화면용. 5개 약관 (terms, privacy, health_data, ai_analysis, marketing) 각각 상태·동의 일시 반환. 각 약관마다 "전문 보기" 링크 제공</t>
         </is>
       </c>
-      <c r="T53" s="27" t="inlineStr">
+      <c r="T53" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="54" ht="199.5" customHeight="1" s="26">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>약관 동의 토글 (선택 약관)</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents/{consent_type}</t>
         </is>
@@ -7204,49 +7214,49 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="H54" s="33" t="inlineStr">
         <is>
           <t>사용자가 마이페이지에서 선택 약관(현재 marketing만 해당)의 동의/철회를 토글한다. 필수 약관(terms, privacy, health_data, ai_analysis)은 본 API로 변경 불가. 필수 약관 철회는 회원탈퇴(DELETE /users/me)를 통해서만 가능.</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="I54" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K54" s="11" t="inlineStr">
+      <c r="K54" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L54" s="11" t="inlineStr">
+      <c r="L54" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M54" s="11" t="inlineStr">
+      <c r="M54" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N54" s="11" t="inlineStr">
+      <c r="N54" s="33" t="inlineStr">
         <is>
           <t>path: consent_type (marketing)</t>
         </is>
       </c>
-      <c r="O54" s="11" t="inlineStr">
+      <c r="O54" s="33" t="inlineStr">
         <is>
           <t>{
   "is_agreed": true
 }</t>
         </is>
       </c>
-      <c r="P54" s="11" t="inlineStr">
+      <c r="P54" s="33" t="inlineStr">
         <is>
           <t>{
   "consent_type": "marketing",
@@ -7256,7 +7266,7 @@
 }</t>
         </is>
       </c>
-      <c r="Q54" s="11" t="inlineStr">
+      <c r="Q54" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 필수 약관은 본 API로 변경 불가 ("필수 약관 철회는 회원탈퇴를 진행해주세요")
@@ -7264,17 +7274,17 @@
 404 존재하지 않는 consent_type</t>
         </is>
       </c>
-      <c r="R54" s="11" t="inlineStr">
+      <c r="R54" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr">
+      <c r="S54" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001 자세히 작성). 마케팅 수신 동의 토글용. 필수 약관(terms·privacy·health_data·ai_analysis)은 400 응답 후 회원탈퇴 안내</t>
         </is>
       </c>
-      <c r="T54" s="27" t="inlineStr">
+      <c r="T54" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -7355,13 +7365,13 @@
       <c r="P55" s="33" t="inlineStr">
         <is>
           <t>{
-  "detail": "인증 코드가 발송되었습니다."
+  "detail": "인증 코드가 이메일로 발송되었습니다."
 }</t>
         </is>
       </c>
       <c r="Q55" s="33" t="inlineStr">
         <is>
-          <t>200 OK / 400 이메일 형식 오류 / 429 발송 쿨다운</t>
+          <t>200 OK / 400 이메일 형식 오류 / 429 발송 쿨다운 (body: {detail, retry_after})</t>
         </is>
       </c>
       <c r="R55" s="33" t="inlineStr">
@@ -7456,7 +7466,7 @@
       <c r="P56" s="33" t="inlineStr">
         <is>
           <t>{
-  "verified": true
+  "detail": "이메일 인증이 완료되었습니다."
 }</t>
         </is>
       </c>
@@ -7954,10 +7964,10 @@
       <c r="P61" s="33" t="inlineStr">
         <is>
           <t>{
-  "medication_alarm": true,
-  "challenge_alarm": true,
   "guide_complete_alarm": true,
-  "push_permission": true
+  "ocr_complete_alarm": true,
+  "system_alarm": true,
+  "updated_at": "2026-06-04T10:00:00Z"
 }</t>
         </is>
       </c>
@@ -8259,14 +8269,12 @@
       <c r="O64" s="33" t="n"/>
       <c r="P64" s="33" t="inlineStr">
         <is>
-          <t>{
-  "detail": "삭제되었습니다."
-}</t>
+          <t>204 No Content (응답 본문 없음)</t>
         </is>
       </c>
       <c r="Q64" s="33" t="inlineStr">
         <is>
-          <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
+          <t>204 No Content / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
       <c r="R64" s="33" t="inlineStr">
@@ -9264,52 +9272,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9319,32 +9327,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/signup</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>회원가입 및 필수 동의 저장</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9354,32 +9362,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/login</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>로그인 및 토큰 발급</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9389,32 +9397,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/logout</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9424,32 +9432,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>내 정보 조회</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9459,32 +9467,32 @@
           <t>PUT</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 저장/수정</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9494,32 +9502,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 조회</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9529,32 +9537,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>의료 이미지 업로드</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9564,32 +9572,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>진료기록 목록 조회</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9599,32 +9607,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>진료기록 상세 조회</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9634,32 +9642,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>/api/v1/ocr/jobs</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>OCR 작업 시작</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9669,32 +9677,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-result</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 조회</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9704,32 +9712,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-text</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 수정</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9739,32 +9747,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/medications/{medication_id}/verify</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>OCR 약품명 확인</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9774,32 +9782,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/search</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>식약처 약품 검색</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9809,32 +9817,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/{drug_id}</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>약품 상세 조회</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9844,32 +9852,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/medications</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>기록별 약품 목록 조회</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9879,32 +9887,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>LLM 복약/생활습관 가이드 생성</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9914,32 +9922,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/{guide_id}</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>가이드 상세 조회</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9949,32 +9957,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/guide</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>기록별 최신 가이드 조회</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9984,32 +9992,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>상담 세션 생성</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10019,32 +10027,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>상담 세션 목록 조회</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10054,32 +10062,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>상담 메시지 목록 조회</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="26">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10089,32 +10097,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>챗봇 메시지 전송 및 답변 생성</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="26">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10124,32 +10132,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>/api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>비동기 작업 상태 조회</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10159,32 +10167,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>/api/v1/feedbacks</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>복약 가이드 피드백 단순 등록</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10194,32 +10202,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>알림 목록 조회</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10229,32 +10237,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/unread-count</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>미읽음 알림 개수 조회</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10264,32 +10272,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}/read</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>알림 읽음 처리</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="26">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10299,17 +10307,17 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
@@ -10946,15 +10954,15 @@
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="26">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10964,32 +10972,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경 ⭐ v3</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="26">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="33" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10999,32 +11007,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회 ⭐ v3</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="26">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -11034,17 +11042,17 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents/{consent_type}</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>약관 동의 토글 (선택 약관) ⭐ v3</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
@@ -12035,84 +12043,84 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>규칙 / 정책</t>
         </is>
       </c>
     </row>
     <row r="5" ht="49.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Base URL</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>/api/v1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>인증 방식</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Bearer Token (JWT). Authorization: Bearer {access_token} 헤더로 전달.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>토큰 정책</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>access_token 유효기간 1시간, refresh_token 유효기간 14일. 5회 연속 로그인 실패 시 10분 잠금.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="49.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Content-Type</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>기본 application/json. 파일 업로드는 multipart/form-data.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="49.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>요청·응답 인코딩</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>UTF-8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="252" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>⭐ 상태코드 정책 v2</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>멘토 피드백 반영: 400으로 통일. 422 사용하지 않음. 
 • 200 OK: 조회·수정 성공
@@ -12132,12 +12140,12 @@
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>⭐ LLM 실패 처리 v2</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>멘토 피드백 반영: "500 LLM 실패" 별도 항목 사용하지 않음.
 • LLM 생성 실패 → processing_jobs.status = 'failed' + error_message 저장
@@ -12148,12 +12156,12 @@
       </c>
     </row>
     <row r="12" ht="54" customHeight="1" s="26">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>⭐ 비동기 작업 응답</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>OCR·LLM은 동기 응답 대신 202 Accepted + job_id 반환.
 클라이언트는 GET /processing-jobs/{job_id}로 상태 폴링.
@@ -12162,12 +12170,12 @@
       </c>
     </row>
     <row r="13" ht="72" customHeight="1" s="26">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>타임아웃 정책</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>• OCR Job: 60초
 • LLM Job: 90초
@@ -12177,12 +12185,12 @@
       </c>
     </row>
     <row r="14" ht="72" customHeight="1" s="26">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>⭐ 식약처 API 출처</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>공공데이터포털 - 식품의약품안전처 의약품 제품 허가 정보
 https://www.data.go.kr/data/15095677/openapi.do
@@ -12192,36 +12200,36 @@
       </c>
     </row>
     <row r="15" ht="49.5" customHeight="1" s="26">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>페이지네이션</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>조회 API는 ?page={n}&amp;size={n} 또는 ?offset={n}&amp;limit={n} 쿼리 파라미터 지원. (챗봇 상담 목록 등은 offset/limit 적용)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="49.5" customHeight="1" s="26">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>요청 검증</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>필수값 누락·타입 오류·비즈니스 검증 실패는 모두 400으로 통일. detail 필드에 사용자에게 표시 가능한 메시지 포함.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="72" customHeight="1" s="26">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>페이로드 검증 예시</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>{
   "detail": "이미 가입된 이메일입니다.",
@@ -12231,48 +12239,48 @@
       </c>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="26">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>민감정보 마스킹</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>로그·에러 응답에 OCR 원문·건강정보·토큰·API Key 노출 금지. 마스킹 또는 출력 제외 처리.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="49.5" customHeight="1" s="26">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>사용자 데이터 격리</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>모든 인증 API는 토큰의 user_id와 리소스의 user_id 검증. 타 사용자 접근 시 403 또는 404 반환.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="49.5" customHeight="1" s="26">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Rate Limit (예정)</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Sprint 3에서 도입 검토. 챗봇 메시지 등 비용 부담 API는 429 응답 + Retry-After 헤더.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="49.5" customHeight="1" s="26">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>API 버전 관리</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>URL 경로에 버전 명시 (/api/v1/...). 호환성 깨지는 변경 시 /v2/ 추가.</t>
         </is>
@@ -13300,259 +13308,259 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>작업 유형</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>트리거 API</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>상태 조회 API</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>타임아웃</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>성공 시</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>실패 시</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>OCR 처리</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/ocr/jobs</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>60초</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>status=completed → ocr_text·medications 후보 저장</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>status=failed 또는 timeout → 사용자에게 재시도 또는 직접 입력 안내</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>식약처 약품 조회</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search (동기 + 캐시)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>(N/A - 동기)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>drug_references 저장 + drug_caches 갱신</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>drug_caches 있으면 캐시 반환 + 마지막 조회 시각 표시 / 없으면 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>LLM 가이드 생성</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/guides</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>90초</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>status=completed → guides·guide_items 저장 + 알림 생성</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>status=failed → 사용자에게 재시도 안내 + 알림 생성</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>챗봇 메시지</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions/{id}/messages (동기, 5초 목표)</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>(N/A - 동기)</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>ssistant_message 즉시 응답 + safety_flag 평가</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>status=failed 응답 + 사용자에게 "답변 생성 실패" 안내</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>RAG 임베딩 (Sprint 3)</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/guideline-sources</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>120초</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>guideline_chunks + embedding_vector 저장</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>embedding_status=failed → 운영자 재시도</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>FHIR 연동 (상용화)</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/fhir/connections</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>fhir_connections.connection_status=connected</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>502 Bad Gateway + retry_count 증가</t>
         </is>
@@ -14573,447 +14581,447 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>평가요건</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>요구사항 ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>관련 API</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>산출물 위치</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4" ht="49.5" customHeight="1" s="26">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>1-1. LLM 기반 안내 가이드 생성</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>REQ-GUIDE-001/002</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>POST /guides, GET /guides/{guide_id}</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>guides·guide_items 테이블, 가이드 결과 화면</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>복약 + 생활습관 가이드 + 의료 안전 고지</t>
         </is>
       </c>
     </row>
     <row r="5" ht="49.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1-2. RAG 파이프라인 (공식협회 기반)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>REQ-RAG-PILOT-001 / REQ-RAG-001</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>POST /guideline-sources, GET /guideline-sources/search</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>guideline_sources·chunks 테이블</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 파일럿 → Sprint 3 pgvector 고도화</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2-1. 실시간 챗봇 (맥락 반영)</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>REQ-CHAT-001/002</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions, POST /chat/sessions/{id}/messages, GET /chat/sessions/{id}/messages</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>chat_sessions·messages 테이블</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>최근 3~5개 메시지 context 포함</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2-2. 챗봇 위험 질문 안전 응답</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>REQ-CHAT-003 / REQ-SAFE-001</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions/{id}/messages (safety_flag)</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>chat_messages.safety_flag</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>키워드 기반 1차 감지 + 상시 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="8" ht="49.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3-1. OCR 기반 의료정보 인식</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001/002</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /ocr/jobs, GET /processing-jobs/{job_id}, GET /records/{id}/ocr-result</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>medical_records·processing_jobs</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Upstage OCR + 라인 단위 저장</t>
         </is>
       </c>
     </row>
     <row r="9" ht="49.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>3-2. OCR 결과 사용자 검수</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-002</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>PATCH /records/{id}/ocr-text, PATCH /medications/{id}/verify</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>medications.is_verified</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>신뢰도 70% 미만 강조</t>
         </is>
       </c>
     </row>
     <row r="10" ht="49.5" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>3-3. 복약알림 (필수 MVP)</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>REQ-NOTI-001</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>GET /notifications, GET /notifications/unread-count, PATCH /notifications/{id}/read, DELETE /notifications/{id}</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>notifications 테이블</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>⭐ v2 P0 상향 (내부 알림함)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="49.5" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>3-4. 피드백 수집 (필수 MVP)</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>REQ-FB-001</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>POST /feedbacks</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>feedbacks 테이블</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>⭐ v2 P0 상향 (가이드·챗봇 피드백)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="49.5" customHeight="1" s="26">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>4-1. 사용자 데이터 접근 제어</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>REQ-SEC-001</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>전체 인증 필요 API</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>user_id 검증 미들웨어</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n"/>
+      <c r="E12" s="36" t="n"/>
     </row>
     <row r="13" ht="49.5" customHeight="1" s="26">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>4-2. 민감정보 보호·로그 마스킹</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>REQ-SEC-002</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>(전체)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>로그 정책 문서</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n"/>
+      <c r="E13" s="36" t="n"/>
     </row>
     <row r="14" ht="49.5" customHeight="1" s="26">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>5-1. API 성능 측정 (P95)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>REQ-NF-002</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>주요 조회 API</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>API 성능 테스트 문서</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>P95 3초 목표</t>
         </is>
       </c>
     </row>
     <row r="15" ht="49.5" customHeight="1" s="26">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>5-2. 비동기 처리</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>REQ-NF-001</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>POST /ocr/jobs, POST /guides, GET /processing-jobs/{id}</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>processing_jobs 테이블</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>타임아웃 관리 포함</t>
         </is>
       </c>
     </row>
     <row r="16" ht="49.5" customHeight="1" s="26">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>5-3. 식약처 API 연동</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/search, GET /drugs/{id}</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>drug_references·drug_caches·api_failure_logs</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>⭐ 공공데이터포털 링크 명시</t>
         </is>
       </c>
     </row>
     <row r="17" ht="49.5" customHeight="1" s="26">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>6-1. 핵심 플로우 (3~5단계)</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>REQ-UX-001</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>전체 화면 흐름</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>와이어프레임 #01~#18 + User Flow</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n"/>
+      <c r="E17" s="36" t="n"/>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="26">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>6-2. 협업·문서화</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>REQ-DOC-001</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>(N/A - 문서)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>R&amp;R, Git, ERD, API 명세서 v2, 와이어프레임</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Git 브랜치 전략 4개</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>3-5. 마이페이지 (계정 관리) ⭐</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 ⭐ v3</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>GET/PATCH /users/me, PATCH password, DELETE /users/me, GET /users/me/consents</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>users 테이블 + user_consents + auth_tokens</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (팀원 피드백)</t>
         </is>
@@ -16039,132 +16047,132 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>핵심 범위 (Sprint 2 MVP)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Git 브랜치</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>돈유정</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>회원가입/로그인/JWT, 사용자/건강 프로필, 의료 문서 업로드, OCR 작업 생성/조회/수정, processing_jobs 상태 조회, 알림 API (P0 상향)</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>feature/backend-auth-ocr</t>
         </is>
       </c>
     </row>
     <row r="6" ht="79.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>신정호</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Backend B (RAG 파이프라인 중심)</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>식약처 API 약품 검색·후보 선택, 챗봇 API, 위험 질문 감지, API 명세서 최신화, 공식협회 기반 RAG 흐름 연결, 피드백 등록 (P0 상향)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>feature/backend-guide-chat</t>
         </is>
       </c>
     </row>
     <row r="7" ht="79.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>조이레</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Frontend + 총괄</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>반응형 웹 화면 전체 (#01~#18), 와이어프레임 기반 UI 구현, API 연결, 알림함·피드백 UI</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>feature/frontend-responsive-web</t>
         </is>
       </c>
     </row>
     <row r="8" ht="79.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>이정훈</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>AI/Infra + 배포</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>OCR API 테스트/구현, LLM 프롬프트 작성, 복약/생활습관 가이드 생성, 챗봇 안전 응답 프롬프트, 위험 질문 키워드, 공통 에러/테스트 케이스, 배포</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>feature/ai-prompt-test</t>
         </is>
       </c>
     </row>
     <row r="9" ht="79.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>유태영</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>멘토</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>기획 리뷰·피드백·평가 항목 점검</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>(N/A)</t>
         </is>
@@ -17192,459 +17200,459 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>상태코드 정책</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>400 / 422 입력값 검증 실패 구분</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>400으로 통일 (모든 입력 오류 포함)</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>멘토: 토스 개발자 센터 참고</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>LLM 실패 처리</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>POST /chat/messages → 500 LLM 실패</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>※ LLM 실패는 job status=failed로 처리 (HTTP 상태가 아닌 비즈니스 상태)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>멘토: 500 LLM 실패 항목 삭제</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>POST /records 응답</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>500 저장 실패 포함</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>500 저장 실패 제거 (서버 내부 오류로 일반화)</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>상태코드 정리</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>/api/v1/admin/operation-logs</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>P3 상용화 검토에 포함</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>API 명세에서 완전 삭제</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>멘토: 운영 로그는 ERD 내부 검토만</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/notifications</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Sprint 3 P2</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>멘토: 복약알림 필수 MVP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/feedbacks</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 Stretch P1</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>멘토: 피드백 필수 MVP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/notifications/unread-count</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>대시보드 알림 뱃지 (멘토: 알림 디테일)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>PATCH /api/v1/notifications/{id}/read</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>내부 알림함 (멘토 피드백)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>DELETE /api/v1/notifications/{id}</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>내부 알림함 (멘토 피드백)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search 비고</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>"식약처 API 호출"</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>+ 공공데이터포털 URL 추가</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>멘토: 식약처 API 데이터셋 링크</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/{drug_id} 비고</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>기본 설명</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>+ 제조사 정보 포함 응답 명시</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>멘토: 제조사 다른 경우 표시</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>/api/v1/challenge-checkins</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Sprint 3 P2</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>확인 완료 — Sprint 3 P2 유지</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>멘토: 확인 요청 답변</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>공통 규칙 시트</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>기본 규칙만</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>+ 상태코드 정책, LLM 실패 처리, 식약처 출처 추가</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>v2 전체 정책 통일</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>20개 시트</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>8개 시트로 통합</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>도메인별 분리 시트들을 우선순위로 통합</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Sprint 우선순위 분류</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Sprint2_MVP_P0, Sprint2_Stretch_P1, Sprint3_P2, Commercial_P3 4개 시트</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>1개 시트로 통합 (단계 컬럼 필터)</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>도메인별 시트</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>회원_사용자, 기록_OCR, 약품_가이드, 챗봇_작업상태, Sprint3_확장, 상용화_검토 6개 시트</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>전체 명세 시트의 도메인 컬럼으로 대체</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
@@ -17659,270 +17667,270 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Before (v2)</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>After (v3)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>POST /auth/login 비고</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>+ 통합 메시지 응답 명시 (계정 존재 노출 방지)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>REQ-AUTH-002 (팀원 보안 피드백)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="26">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>GET /records/{id}/ocr 비고</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>+ medications[].manufacturer 필수 명시</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="26">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/search 비고</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>식약처 API 호출</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>+ manufacturer 필수 필드 ("제조사 정보 없음" 폴백)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/{id} 비고</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>+ manufacturer 필수 필드 명시</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>POST /records 비고</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>image_expires_at 90일 보존</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>+ REQ-REC-001과 일치 확인 완료 추가</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>팀원 피드백: 요구사항·API 일치 확인</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>전체 API 수</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>47개</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>49개 (+2 마이페이지)</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 신규</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0 API 수</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>29개</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>31개 (+2 마이페이지)</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>마이페이지 P0</t>
         </is>
@@ -17937,216 +17945,216 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="26">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="26">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 상세 요구사항</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>7개 메뉴 간단 나열</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>10개 메뉴 + 비밀번호 변경 4단계 + 회원탈퇴 5단계 + 약관 5개 관리 상세</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>팀원: 마이페이지 자세히 작성</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="26">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password 비고</t>
         </is>
       </c>
-      <c r="C37" s="25" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>+ 4단계 흐름, 5회 실패 10분 제한, 이메일·이름·닉네임 동일 제한</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>비밀번호 변경 상세화</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="26">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>DELETE /users/me 비고</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>+ 5단계 흐름, 5회 실패 24시간 제한, OCR/LLM cancelled, 30일 영구 삭제 배치</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>회원탈퇴 상세화</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="26">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents 비고</t>
         </is>
       </c>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>+ 5개 약관 (terms/privacy/health_data/ai_analysis/marketing), 전문 보기</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>약관 관리 상세화</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="26">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me 비고</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>+ 30일 1회 변경 제한, 욕설 필터링, 다음 변경 가능일 메시지</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>닉네임 정책 명시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="26">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/consents/{type}</t>
         </is>
       </c>
-      <c r="C41" s="25" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>신규 추가 (선택 약관 토글, 필수 약관은 400)</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="36" t="inlineStr">
         <is>
           <t>마케팅 수신 토글용</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="26">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t>전체 API 개수</t>
         </is>
       </c>
-      <c r="C42" s="25" t="inlineStr">
+      <c r="C42" s="36" t="inlineStr">
         <is>
           <t>49개</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>50개 (+1)</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
         <is>
           <t>약관 토글 추가</t>
         </is>

--- a/docs/api/api-spec-final.xlsx
+++ b/docs/api/api-spec-final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. v3 팀원 피드백 API 수정" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. 전체 API 명세 v3" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Sprint 우선순위 분류" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 공통 규칙 v2" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 비동기 처리 흐름" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. 평가요건 매핑" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. 담당자 역할 기준" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. 변경 이력" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="0. v3 팀원 피드백 API 수정" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1. 전체 API 명세 v3" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2. Sprint 우선순위 분류" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3. 공통 규칙 v2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="4. 비동기 처리 흐름" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5. 평가요건 매핑" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="6. 담당자 역할 기준" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7. 변경 이력" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,119 +575,119 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>팀원 피드백</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>API 변경 내역</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 마이페이지 요구사항 신규 추가</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>PATCH /api/v1/users/me/password 신규 추가 (P0)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/users/me/consents 신규 추가 (P0)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>REQ-AUTH-002 로그인 메시지 보안 강화</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/auth/login Error Response 비고 업데이트</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>REQ-REC-001 이미지 보관 90일 확정</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/records 비고는 이미 90일로 명시 (변경 불필요)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001 약품 카드 제조사 포함</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/records/{record_id}/ocr 응답 스키마에 manufacturer 명시</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 제조사 무조건 표기</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search, /drugs/{id} 응답 스키마에 manufacturer 필수 명시</t>
         </is>
@@ -701,81 +701,81 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>관련 요구사항</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="33" t="inlineStr">
         <is>
           <t>PATCH</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 / P0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 / P0</t>
         </is>
@@ -789,102 +789,102 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>영역</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>v3</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>전체 API 개수</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="36" t="inlineStr">
         <is>
           <t>47개</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="36" t="inlineStr">
         <is>
           <t>49개 (+2)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0 API</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="36" t="inlineStr">
         <is>
           <t>29개</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="36" t="inlineStr">
         <is>
           <t>31개 (+2 마이페이지)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>마이페이지 도메인</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>GET/PATCH/DELETE /users/me (3개)</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>+ PATCH password + GET consents (5개)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>로그인 보안</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>구분 메시지</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>통합 메시지 (계정 존재 노출 방지)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>약품 응답</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>제조사 선택적</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>manufacturer 필수 필드 명시</t>
         </is>
@@ -899,119 +899,119 @@
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>변경 내용</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>관련 API</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 — 메뉴 10개·비밀번호 변경 4단계·회원탈퇴 5단계 상세 명시</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>(요구사항 정의서 본문)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>비밀번호 변경 API 비고 보강 (4단계 흐름, 5회 실패 10분 제한, 모든 기기 로그아웃)</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>회원탈퇴 API 비고 보강 (5단계 흐름, 5회 실패 24시간 제한, OCR/LLM cancelled, 30일 영구 삭제)</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>DELETE /users/me</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="26">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>약관 동의 조회 API 비고 보강 (5개 약관 + 전문 보기 링크)</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="26">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>닉네임 수정 API 비고 보강 (30일 1회 제한, 욕설 필터링)</t>
         </is>
       </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="26">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>선택 약관 토글 API 신규 추가 (마케팅 수신 동의/철회)</t>
         </is>
       </c>
-      <c r="C35" s="25" t="inlineStr">
+      <c r="C35" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/consents/{consent_type} ⭐ 신규</t>
         </is>
@@ -2034,132 +2034,132 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" s="26">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>기능 단계</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>도메인</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>API명</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>Request URL</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>HTTP Method</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>인증 필요</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="35" t="inlineStr">
         <is>
           <t>비동기 여부</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="35" t="inlineStr">
         <is>
           <t>협업</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="35" t="inlineStr">
         <is>
           <t>Header Schema</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="35" t="inlineStr">
         <is>
           <t>Query Parameter Schema</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="O4" s="35" t="inlineStr">
         <is>
           <t>Request Body Example</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="P4" s="35" t="inlineStr">
         <is>
           <t>Success Response Example</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="Q4" s="35" t="inlineStr">
         <is>
           <t>Error Response / Status Code</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="R4" s="35" t="inlineStr">
         <is>
           <t>관련 ERD 테이블</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="35" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="35" t="inlineStr">
         <is>
           <t>완료 상태</t>
         </is>
       </c>
     </row>
     <row r="5" ht="127.5" customHeight="1" s="26">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>회원가입 및 필수 동의 저장</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/signup</t>
         </is>
@@ -2169,38 +2169,38 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>이메일 회원가입과 필수 약관/민감정보/AI 분석 동의를 한 번에 저장한다.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t>Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t>{
   "email": "user@example.com",
@@ -2228,7 +2228,7 @@
 }</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t>{
   "user_id": 1,
@@ -2237,52 +2237,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 필수값 누락 / 409 이메일 중복</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="33" t="inlineStr">
         <is>
           <t>users, user_consents</t>
         </is>
       </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t>이메일 형식, 비밀번호 정책 검증 포함</t>
         </is>
       </c>
-      <c r="T5" s="27" t="inlineStr">
+      <c r="T5" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>로그인 및 토큰 발급</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/login</t>
         </is>
@@ -2292,38 +2292,38 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>로그인 성공 시 access_token과 refresh_token을 발급한다.</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="33" t="inlineStr">
         <is>
           <t>Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N6" s="11" t="n"/>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="inlineStr">
         <is>
           <t>{
   "email": "user@example.com",
@@ -2331,7 +2331,7 @@
 }</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t>{
   "access_token": "jwt.access",
@@ -2344,7 +2344,7 @@
 }</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 입력 오류
@@ -2352,47 +2352,47 @@
 429 5회 연속 실패 잠금</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr">
+      <c r="R6" s="33" t="inlineStr">
         <is>
           <t>users, auth_tokens</t>
         </is>
       </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="S6" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 팀원 피드백: 개인정보 보안 — 401 응답 시 계정 없음/비밀번호 불일치 구분 없이 통합 메시지</t>
         </is>
       </c>
-      <c r="T6" s="27" t="inlineStr">
+      <c r="T6" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>회원/인증</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/logout</t>
         </is>
@@ -2402,93 +2402,93 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>현재 refresh token을 revoke 처리한다.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="inlineStr">
+      <c r="N7" s="33" t="n"/>
+      <c r="O7" s="33" t="inlineStr">
         <is>
           <t>{
   "refresh_token": "jwt.refresh"
 }</t>
         </is>
       </c>
-      <c r="P7" s="11" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "로그아웃되었습니다."
 }</t>
         </is>
       </c>
-      <c r="Q7" s="11" t="inlineStr">
+      <c r="Q7" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R7" s="11" t="inlineStr">
+      <c r="R7" s="33" t="inlineStr">
         <is>
           <t>auth_tokens</t>
         </is>
       </c>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="27" t="inlineStr">
+      <c r="S7" s="33" t="n"/>
+      <c r="T7" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>내 정보 조회</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me</t>
         </is>
@@ -2498,39 +2498,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>로그인한 사용자의 기본 정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L8" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N8" s="11" t="n"/>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="N8" s="33" t="n"/>
+      <c r="O8" s="33" t="n"/>
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t>{
   "user_id": 1,
@@ -2541,48 +2541,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q8" s="11" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R8" s="11" t="inlineStr">
+      <c r="R8" s="33" t="inlineStr">
         <is>
           <t>users</t>
         </is>
       </c>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="27" t="inlineStr">
+      <c r="S8" s="33" t="n"/>
+      <c r="T8" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="9" ht="63.75" customHeight="1" s="26">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>건강정보</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 저장/수정</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
@@ -2592,39 +2592,39 @@
           <t>PUT</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드와 챗봇 context에 사용할 최소 건강정보를 저장한다.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J9" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L9" s="11" t="inlineStr">
+      <c r="L9" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="M9" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N9" s="11" t="n"/>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="N9" s="33" t="n"/>
+      <c r="O9" s="33" t="inlineStr">
         <is>
           <t>{
   "age_group": "30s",
@@ -2643,7 +2643,7 @@
 }</t>
         </is>
       </c>
-      <c r="P9" s="11" t="inlineStr">
+      <c r="P9" s="33" t="inlineStr">
         <is>
           <t>{
   "profile_id": 1,
@@ -2651,48 +2651,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q9" s="11" t="inlineStr">
+      <c r="Q9" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 잘못된 입력 / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R9" s="11" t="inlineStr">
+      <c r="R9" s="33" t="inlineStr">
         <is>
           <t>user_health_profiles</t>
         </is>
       </c>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="27" t="inlineStr">
+      <c r="S9" s="33" t="n"/>
+      <c r="T9" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="26">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>건강정보</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 조회</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
@@ -2702,39 +2702,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="33" t="inlineStr">
         <is>
           <t>현재 로그인 사용자의 건강정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="J10" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="M10" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N10" s="11" t="n"/>
-      <c r="O10" s="11" t="n"/>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="N10" s="33" t="n"/>
+      <c r="O10" s="33" t="n"/>
+      <c r="P10" s="33" t="inlineStr">
         <is>
           <t>{
   "profile_id": 1,
@@ -2750,48 +2750,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q10" s="11" t="inlineStr">
+      <c r="Q10" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 404 프로필 없음</t>
         </is>
       </c>
-      <c r="R10" s="11" t="inlineStr">
+      <c r="R10" s="33" t="inlineStr">
         <is>
           <t>user_health_profiles</t>
         </is>
       </c>
-      <c r="S10" s="11" t="n"/>
-      <c r="T10" s="27" t="inlineStr">
+      <c r="S10" s="33" t="n"/>
+      <c r="T10" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="26">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>의료 이미지 업로드</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
@@ -2801,45 +2801,45 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>처방전/약봉투/진료기록 이미지 또는 PDF를 업로드하고 record_id를 생성한다.</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J11" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="L11" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: multipart/form-data</t>
         </is>
       </c>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="N11" s="33" t="n"/>
+      <c r="O11" s="33" t="inlineStr">
         <is>
           <t>file: binary
 record_type: prescription|medicine_bag|medical_record</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -2850,52 +2850,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q11" s="11" t="inlineStr">
+      <c r="Q11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">201 Created / 400 파일 형식 오류 / 401 인증 실패 / 413 용량 초과 </t>
         </is>
       </c>
-      <c r="R11" s="11" t="inlineStr">
+      <c r="R11" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="33" t="inlineStr">
         <is>
           <t>image_expires_at 90일 보존 정책 반영 | ⭐ v3: 요구사항 REQ-REC-001과 90일 정책 일치 확인 완료 (팀원 피드백)</t>
         </is>
       </c>
-      <c r="T11" s="27" t="inlineStr">
+      <c r="T11" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="12" ht="60" customHeight="1" s="26">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>진료기록 목록 조회</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
@@ -2905,43 +2905,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>사용자의 업로드 기록 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J12" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K12" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L12" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="M12" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N12" s="33" t="inlineStr">
         <is>
           <t>page, size, record_type</t>
         </is>
       </c>
-      <c r="O12" s="11" t="n"/>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="O12" s="33" t="n"/>
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -2957,48 +2957,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="Q12" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R12" s="11" t="inlineStr">
+      <c r="R12" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="27" t="inlineStr">
+      <c r="S12" s="33" t="n"/>
+      <c r="T12" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1" s="26">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>진료기록 상세 조회</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}</t>
         </is>
@@ -3008,39 +3008,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>record_id 기준으로 업로드 정보와 처리 상태를 조회한다.</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I13" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K13" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L13" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="M13" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n"/>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="N13" s="33" t="n"/>
+      <c r="O13" s="33" t="n"/>
+      <c r="P13" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3050,48 +3050,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q13" s="11" t="inlineStr">
+      <c r="Q13" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 타 사용자 기록 접근 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R13" s="11" t="inlineStr">
+      <c r="R13" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="27" t="inlineStr">
+      <c r="S13" s="33" t="n"/>
+      <c r="T13" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1" s="26">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>OCR 작업 시작</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>/api/v1/ocr/jobs</t>
         </is>
@@ -3101,39 +3101,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="33" t="inlineStr">
         <is>
           <t>업로드된 record_id에 대해 OCR 비동기 작업을 시작하고 job_id를 반환한다.</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="L14" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="11" t="inlineStr">
+      <c r="N14" s="33" t="n"/>
+      <c r="O14" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3141,7 +3141,7 @@
 }</t>
         </is>
       </c>
-      <c r="P14" s="11" t="inlineStr">
+      <c r="P14" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 101,
@@ -3151,52 +3151,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="Q14" s="33" t="inlineStr">
         <is>
           <t>202 Accepted / 400 잘못된 record_id / 401 인증 실패 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R14" s="11" t="inlineStr">
+      <c r="R14" s="33" t="inlineStr">
         <is>
           <t>processing_jobs, medical_records</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="S14" s="33" t="inlineStr">
         <is>
           <t>P95 3초 대응을 위해 job_id 반환 방식</t>
         </is>
       </c>
-      <c r="T14" s="27" t="inlineStr">
+      <c r="T14" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="26">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 조회</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-result</t>
         </is>
@@ -3206,39 +3206,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="33" t="inlineStr">
         <is>
           <t>OCR 원문, 편집본, 신뢰도, 약품 후보를 조회한다.</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
+      <c r="J15" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="K15" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L15" s="11" t="inlineStr">
+      <c r="L15" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n"/>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="N15" s="33" t="n"/>
+      <c r="O15" s="33" t="n"/>
+      <c r="P15" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3255,52 +3255,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 타 사용자 기록 접근 / 404 결과 없음</t>
         </is>
       </c>
-      <c r="R15" s="11" t="inlineStr">
+      <c r="R15" s="33" t="inlineStr">
         <is>
           <t>medical_records, medications</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="S15" s="33" t="inlineStr">
         <is>
           <t>⭐ v3: 응답에 medications[].manufacturer 필수 포함 (팀원 피드백)</t>
         </is>
       </c>
-      <c r="T15" s="27" t="inlineStr">
+      <c r="T15" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="16" ht="60" customHeight="1" s="26">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 수정</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-text</t>
         </is>
@@ -3310,46 +3310,46 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="33" t="inlineStr">
         <is>
           <t>사용자가 OCR 결과를 확인/수정하고 저장한다.</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J16" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L16" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="M16" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N16" s="11" t="n"/>
-      <c r="O16" s="11" t="inlineStr">
+      <c r="N16" s="33" t="n"/>
+      <c r="O16" s="33" t="inlineStr">
         <is>
           <t>{
   "ocr_edited_text": "타이레놀 500mg 1정 식후 복용"
 }</t>
         </is>
       </c>
-      <c r="P16" s="11" t="inlineStr">
+      <c r="P16" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3358,48 +3358,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q16" s="11" t="inlineStr">
+      <c r="Q16" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 입력값 오류 / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R16" s="11" t="inlineStr">
+      <c r="R16" s="33" t="inlineStr">
         <is>
           <t>medical_records</t>
         </is>
       </c>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="27" t="inlineStr">
+      <c r="S16" s="33" t="n"/>
+      <c r="T16" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1" s="26">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="33" t="inlineStr">
         <is>
           <t>진료기록/OCR</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>OCR 약품명 확인</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/medications/{medication_id}/verify</t>
         </is>
@@ -3409,39 +3409,39 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="33" t="inlineStr">
         <is>
           <t>OCR 신뢰도 낮은 약품명을 사용자가 확인하고 is_verified를 true로 저장한다.</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J17" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K17" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L17" s="11" t="inlineStr">
+      <c r="L17" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="M17" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="inlineStr">
+      <c r="N17" s="33" t="n"/>
+      <c r="O17" s="33" t="inlineStr">
         <is>
           <t>{
   "drug_name": "타이레놀정500mg",
@@ -3449,7 +3449,7 @@
 }</t>
         </is>
       </c>
-      <c r="P17" s="11" t="inlineStr">
+      <c r="P17" s="33" t="inlineStr">
         <is>
           <t>{
   "medication_id": 30,
@@ -3458,52 +3458,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q17" s="11" t="inlineStr">
+      <c r="Q17" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 입력 오류 / 401 인증 실패 / 404 약품 없음</t>
         </is>
       </c>
-      <c r="R17" s="11" t="inlineStr">
+      <c r="R17" s="33" t="inlineStr">
         <is>
           <t>medications</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="33" t="inlineStr">
         <is>
           <t>신뢰도 기준 미만 후보를 사용자 확인 대상으로 표시</t>
         </is>
       </c>
-      <c r="T17" s="27" t="inlineStr">
+      <c r="T17" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="18" ht="60" customHeight="1" s="26">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>식약처 약품 검색</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/search</t>
         </is>
@@ -3513,43 +3513,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="33" t="inlineStr">
         <is>
           <t>약품명, 일반명, 성분명 기준으로 식약처 API 또는 캐시에서 약품을 검색한다.</t>
         </is>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J18" s="11" t="inlineStr">
+      <c r="J18" s="33" t="inlineStr">
         <is>
           <t>부분 비동기</t>
         </is>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="L18" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="M18" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
+      <c r="N18" s="33" t="inlineStr">
         <is>
           <t>q, search_type, page, size</t>
         </is>
       </c>
-      <c r="O18" s="11" t="n"/>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="O18" s="33" t="n"/>
+      <c r="P18" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -3563,52 +3563,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q18" s="11" t="inlineStr">
+      <c r="Q18" s="33" t="inlineStr">
         <is>
           <t>200 OK / 400 검색어 누락 / 401 인증 실패 / 504 외부 API timeout</t>
         </is>
       </c>
-      <c r="R18" s="11" t="inlineStr">
+      <c r="R18" s="33" t="inlineStr">
         <is>
           <t>drug_references, drug_caches, api_failure_logs</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="33" t="inlineStr">
         <is>
           <t>⭐ 식약처 의약품안전나라 (공공데이터포털): https://www.data.go.kr/data/15095677/openapi.do | 일반명↔상품명 양방향 검색, 캐시 7일 | ⭐ v3: 응답 스키마에 manufacturer 필수 필드 (누락 시 "제조사 정보 없음")</t>
         </is>
       </c>
-      <c r="T18" s="27" t="inlineStr">
+      <c r="T18" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1" s="26">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>약품 상세 조회</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/{drug_id}</t>
         </is>
@@ -3618,39 +3618,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
         <is>
           <t>식약처 기준 약품 상세 정보를 조회한다.</t>
         </is>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K19" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="L19" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="M19" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="inlineStr">
+      <c r="N19" s="33" t="n"/>
+      <c r="O19" s="33" t="n"/>
+      <c r="P19" s="33" t="inlineStr">
         <is>
           <t>{
   "drug_ref_id": 100,
@@ -3662,52 +3662,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q19" s="11" t="inlineStr">
+      <c r="Q19" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 404 약품 없음</t>
         </is>
       </c>
-      <c r="R19" s="11" t="inlineStr">
+      <c r="R19" s="33" t="inlineStr">
         <is>
           <t>drug_references</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="S19" s="33" t="inlineStr">
         <is>
           <t>⭐ 식약처 의약품 제품 허가정보. 제조사 정보 포함 응답 | ⭐ v3: manufacturer 필수 필드 명시</t>
         </is>
       </c>
-      <c r="T19" s="27" t="inlineStr">
+      <c r="T19" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1" s="26">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="33" t="inlineStr">
         <is>
           <t>약품</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>기록별 약품 목록 조회</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/medications</t>
         </is>
@@ -3717,39 +3717,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="33" t="inlineStr">
         <is>
           <t>OCR 또는 직접 입력으로 추출/저장된 약품 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K20" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L20" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="M20" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N20" s="11" t="n"/>
-      <c r="O20" s="11" t="n"/>
-      <c r="P20" s="11" t="inlineStr">
+      <c r="N20" s="33" t="n"/>
+      <c r="O20" s="33" t="n"/>
+      <c r="P20" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3765,17 +3765,17 @@
 }</t>
         </is>
       </c>
-      <c r="Q20" s="11" t="inlineStr">
+      <c r="Q20" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
-      <c r="R20" s="11" t="inlineStr">
+      <c r="R20" s="33" t="inlineStr">
         <is>
           <t>medications</t>
         </is>
       </c>
-      <c r="S20" s="11" t="inlineStr">
+      <c r="S20" s="33" t="inlineStr">
         <is>
           <t>⭐ v4: 미구현 — ocr-result의 medication_candidates로 대체 추정 (확인 필요)</t>
         </is>
@@ -3787,30 +3787,30 @@
       </c>
     </row>
     <row r="21" ht="60" customHeight="1" s="26">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>LLM 복약/생활습관 가이드 생성</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/generate</t>
         </is>
@@ -3820,39 +3820,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="33" t="inlineStr">
         <is>
           <t>OCR 수정본, 약품 정보, 건강정보를 context로 LLM 가이드 생성 작업을 시작한다.</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L21" s="11" t="inlineStr">
+      <c r="L21" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="M21" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="11" t="inlineStr">
+      <c r="N21" s="33" t="n"/>
+      <c r="O21" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -3860,7 +3860,7 @@
 }</t>
         </is>
       </c>
-      <c r="P21" s="11" t="inlineStr">
+      <c r="P21" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 201,
@@ -3869,53 +3869,53 @@
 }</t>
         </is>
       </c>
-      <c r="Q21" s="11" t="inlineStr">
+      <c r="Q21" s="33" t="inlineStr">
         <is>
           <t>202 Accepted / 400 입력 오류 / 401 인증 실패 / 404 record 없음 / 504 LLM timeout</t>
         </is>
       </c>
-      <c r="R21" s="11" t="inlineStr">
+      <c r="R21" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items, processing_jobs</t>
         </is>
       </c>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="S21" s="33" t="inlineStr">
         <is>
           <t>model_name, prompt_version 저장
 ⭐ v4: 실제 경로 /guides → /guides/generate 반영</t>
         </is>
       </c>
-      <c r="T21" s="27" t="inlineStr">
+      <c r="T21" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="22" ht="63.75" customHeight="1" s="26">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>가이드 상세 조회</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/{guide_id}</t>
         </is>
@@ -3925,39 +3925,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="33" t="inlineStr">
         <is>
           <t>생성된 복약/생활습관 가이드와 항목별 guide_items를 조회한다.</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr">
+      <c r="K22" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="L22" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="M22" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="11" t="n"/>
-      <c r="P22" s="11" t="inlineStr">
+      <c r="N22" s="33" t="n"/>
+      <c r="O22" s="33" t="n"/>
+      <c r="P22" s="33" t="inlineStr">
         <is>
           <t>{
   "guide_id": 50,
@@ -3977,48 +3977,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q22" s="11" t="inlineStr">
+      <c r="Q22" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 가이드 없음</t>
         </is>
       </c>
-      <c r="R22" s="11" t="inlineStr">
+      <c r="R22" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items</t>
         </is>
       </c>
-      <c r="S22" s="11" t="n"/>
-      <c r="T22" s="27" t="inlineStr">
+      <c r="S22" s="33" t="n"/>
+      <c r="T22" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="23" ht="60" customHeight="1" s="26">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>LLM 가이드</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>기록별 최신 가이드 조회</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/guide</t>
         </is>
@@ -4028,39 +4028,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="33" t="inlineStr">
         <is>
           <t>record_id 기준 최신 가이드 결과를 조회한다.</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J23" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="K23" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L23" s="11" t="inlineStr">
+      <c r="L23" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="M23" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11" t="n"/>
-      <c r="P23" s="11" t="inlineStr">
+      <c r="N23" s="33" t="n"/>
+      <c r="O23" s="33" t="n"/>
+      <c r="P23" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -4070,17 +4070,17 @@
 }</t>
         </is>
       </c>
-      <c r="Q23" s="11" t="inlineStr">
+      <c r="Q23" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 가이드 없음</t>
         </is>
       </c>
-      <c r="R23" s="11" t="inlineStr">
+      <c r="R23" s="33" t="inlineStr">
         <is>
           <t>guides, guide_items</t>
         </is>
       </c>
-      <c r="S23" s="11" t="inlineStr">
+      <c r="S23" s="33" t="inlineStr">
         <is>
           <t>⭐ v4: 미구현 — GET /guides/{guide_id}로 대체 (확인 필요)</t>
         </is>
@@ -4092,30 +4092,30 @@
       </c>
     </row>
     <row r="24" ht="60" customHeight="1" s="26">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>상담 세션 생성</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
@@ -4125,39 +4125,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="33" t="inlineStr">
         <is>
           <t>record_id 또는 guide_id와 연결된 상담 세션을 생성한다.</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J24" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K24" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L24" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="M24" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="11" t="inlineStr">
+      <c r="N24" s="33" t="n"/>
+      <c r="O24" s="33" t="inlineStr">
         <is>
           <t>{
   "record_id": 10,
@@ -4166,7 +4166,7 @@
 }</t>
         </is>
       </c>
-      <c r="P24" s="11" t="inlineStr">
+      <c r="P24" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4175,48 +4175,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q24" s="11" t="inlineStr">
+      <c r="Q24" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 입력 오류 / 401 인증 실패 / 403 권한 없음</t>
         </is>
       </c>
-      <c r="R24" s="11" t="inlineStr">
+      <c r="R24" s="33" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="27" t="inlineStr">
+      <c r="S24" s="33" t="n"/>
+      <c r="T24" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1" s="26">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>상담 세션 목록 조회</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
@@ -4226,43 +4226,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="33" t="inlineStr">
         <is>
           <t>로그인 사용자의 상담 세션 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J25" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K25" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L25" s="11" t="inlineStr">
+      <c r="L25" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="M25" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="N25" s="33" t="inlineStr">
         <is>
           <t>offset, limit</t>
         </is>
       </c>
-      <c r="O25" s="11" t="n"/>
-      <c r="P25" s="11" t="inlineStr">
+      <c r="O25" s="33" t="n"/>
+      <c r="P25" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -4291,48 +4291,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q25" s="11" t="inlineStr">
+      <c r="Q25" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R25" s="11" t="inlineStr">
+      <c r="R25" s="33" t="inlineStr">
         <is>
           <t>chat_sessions</t>
         </is>
       </c>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="27" t="inlineStr">
+      <c r="S25" s="33" t="n"/>
+      <c r="T25" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="26" ht="63.75" customHeight="1" s="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>상담 메시지 목록 조회</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
@@ -4342,43 +4342,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="33" t="inlineStr">
         <is>
           <t>특정 상담 세션의 메시지를 시간순으로 조회한다.</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K26" s="11" t="inlineStr">
+      <c r="K26" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="L26" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M26" s="11" t="inlineStr">
+      <c r="M26" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N26" s="11" t="inlineStr">
+      <c r="N26" s="33" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="O26" s="11" t="n"/>
-      <c r="P26" s="11" t="inlineStr">
+      <c r="O26" s="33" t="n"/>
+      <c r="P26" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4406,48 +4406,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q26" s="11" t="inlineStr">
+      <c r="Q26" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 세션 없음</t>
         </is>
       </c>
-      <c r="R26" s="11" t="inlineStr">
+      <c r="R26" s="33" t="inlineStr">
         <is>
           <t>chat_sessions, chat_messages</t>
         </is>
       </c>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="27" t="inlineStr">
+      <c r="S26" s="33" t="n"/>
+      <c r="T26" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="27" ht="63.75" customHeight="1" s="26">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="33" t="inlineStr">
         <is>
           <t>실시간 챗봇</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>챗봇 메시지 전송 및 답변 생성</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
@@ -4457,39 +4457,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="33" t="inlineStr">
         <is>
           <t>사용자 질문을 저장하고 최근 3~5개 메시지를 context로 LLM 또는 규칙 기반 답변을 생성한다.</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J27" s="11" t="inlineStr">
+      <c r="J27" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K27" s="11" t="inlineStr">
+      <c r="K27" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L27" s="11" t="inlineStr">
+      <c r="L27" s="33" t="inlineStr">
         <is>
           <t>AI/Infra, Frontend</t>
         </is>
       </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="M27" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N27" s="11" t="n"/>
-      <c r="O27" s="11" t="inlineStr">
+      <c r="N27" s="33" t="n"/>
+      <c r="O27" s="33" t="inlineStr">
         <is>
           <t>{
   "message": "이 약을 식후에 먹어도 되나요?",
@@ -4498,7 +4498,7 @@
 }</t>
         </is>
       </c>
-      <c r="P27" s="11" t="inlineStr">
+      <c r="P27" s="33" t="inlineStr">
         <is>
           <t>{
   "session_id": 70,
@@ -4509,52 +4509,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q27" s="11" t="inlineStr">
+      <c r="Q27" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 질문 누락 / 401 인증 실패 / 403 권한 없음 / 429 요청 횟수 초과 / ※ LLM 실패는 job status=failed로 처리</t>
         </is>
       </c>
-      <c r="R27" s="11" t="inlineStr">
+      <c r="R27" s="33" t="inlineStr">
         <is>
           <t>chat_messages, chat_sessions</t>
         </is>
       </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="S27" s="33" t="inlineStr">
         <is>
           <t>위험 질문은 safety_flag=true 및 의료기관 상담 권고</t>
         </is>
       </c>
-      <c r="T27" s="27" t="inlineStr">
+      <c r="T27" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="28" ht="60" customHeight="1" s="26">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="33" t="inlineStr">
         <is>
           <t>작업 상태</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>비동기 작업 상태 조회</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>/api/v1/processing-jobs/{job_id}</t>
         </is>
@@ -4564,39 +4564,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="33" t="inlineStr">
         <is>
           <t>OCR, 약품 조회, 가이드 생성 등 비동기 작업 상태를 조회한다.</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K28" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L28" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="M28" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N28" s="11" t="n"/>
-      <c r="O28" s="11" t="n"/>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="N28" s="33" t="n"/>
+      <c r="O28" s="33" t="n"/>
+      <c r="P28" s="33" t="inlineStr">
         <is>
           <t>{
   "job_id": 101,
@@ -4609,48 +4609,48 @@
 }</t>
         </is>
       </c>
-      <c r="Q28" s="11" t="inlineStr">
+      <c r="Q28" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 job 없음</t>
         </is>
       </c>
-      <c r="R28" s="11" t="inlineStr">
+      <c r="R28" s="33" t="inlineStr">
         <is>
           <t>processing_jobs</t>
         </is>
       </c>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="27" t="inlineStr">
+      <c r="S28" s="33" t="n"/>
+      <c r="T28" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="29" ht="60" customHeight="1" s="26">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="33" t="inlineStr">
         <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>복약 가이드 피드백 단순 등록</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>/api/v1/feedbacks</t>
         </is>
@@ -4660,39 +4660,39 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="33" t="inlineStr">
         <is>
           <t>가이드 또는 챗봇 답변에 대한 별점/코멘트를 등록한다.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K29" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
-      <c r="L29" s="11" t="inlineStr">
+      <c r="L29" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="M29" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}
 Content-Type: application/json</t>
         </is>
       </c>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="11" t="inlineStr">
+      <c r="N29" s="33" t="n"/>
+      <c r="O29" s="33" t="inlineStr">
         <is>
           <t>{
   "guide_id": 50,
@@ -4703,7 +4703,7 @@
 }</t>
         </is>
       </c>
-      <c r="P29" s="11" t="inlineStr">
+      <c r="P29" s="33" t="inlineStr">
         <is>
           <t>{
   "feedback_id": 300,
@@ -4711,17 +4711,17 @@
 }</t>
         </is>
       </c>
-      <c r="Q29" s="11" t="inlineStr">
+      <c r="Q29" s="33" t="inlineStr">
         <is>
           <t>201 Created / 400 입력 오류 / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R29" s="11" t="inlineStr">
+      <c r="R29" s="33" t="inlineStr">
         <is>
           <t>feedbacks</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr">
+      <c r="S29" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 멘토 반영: P1 → P0 상향 (가이드·챗봇 피드백 등록 필수 MVP)
 ⭐ v4: 미구현(미착수) — 구현 여부 확인 필요</t>
@@ -4734,30 +4734,30 @@
       </c>
     </row>
     <row r="30" ht="60" customHeight="1" s="26">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>알림 목록 조회</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications</t>
         </is>
@@ -4767,43 +4767,43 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="33" t="inlineStr">
         <is>
           <t>사용자 알림 목록을 조회한다.</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J30" s="11" t="inlineStr">
+      <c r="J30" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="K30" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="L30" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="M30" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N30" s="11" t="inlineStr">
+      <c r="N30" s="33" t="inlineStr">
         <is>
           <t>page, size, is_read</t>
         </is>
       </c>
-      <c r="O30" s="11" t="n"/>
-      <c r="P30" s="11" t="inlineStr">
+      <c r="O30" s="33" t="n"/>
+      <c r="P30" s="33" t="inlineStr">
         <is>
           <t>{
   "items": [
@@ -4816,52 +4816,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q30" s="11" t="inlineStr">
+      <c r="Q30" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R30" s="11" t="inlineStr">
+      <c r="R30" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
+      <c r="S30" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 멘토 반영: P2 → P0 상향 (내부 알림함 필수 MVP)</t>
         </is>
       </c>
-      <c r="T30" s="27" t="inlineStr">
+      <c r="T30" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="31" ht="60" customHeight="1" s="26">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>미읽음 알림 개수 조회</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/unread-count</t>
         </is>
@@ -4871,91 +4871,91 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="33" t="inlineStr">
         <is>
           <t>대시보드 알림 아이콘 뱃지에 표시할 미읽음 알림 개수를 반환한다.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J31" s="11" t="inlineStr">
+      <c r="J31" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K31" s="11" t="inlineStr">
+      <c r="K31" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L31" s="11" t="inlineStr">
+      <c r="L31" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="M31" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="11" t="n"/>
-      <c r="P31" s="11" t="inlineStr">
+      <c r="N31" s="33" t="n"/>
+      <c r="O31" s="33" t="n"/>
+      <c r="P31" s="33" t="inlineStr">
         <is>
           <t>{
   "unread_count": 5
 }</t>
         </is>
       </c>
-      <c r="Q31" s="11" t="inlineStr">
+      <c r="Q31" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패</t>
         </is>
       </c>
-      <c r="R31" s="11" t="inlineStr">
+      <c r="R31" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="S31" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백): 대시보드 미읽음 뱃지용</t>
         </is>
       </c>
-      <c r="T31" s="27" t="inlineStr">
+      <c r="T31" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="32" ht="60" customHeight="1" s="26">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>알림 읽음 처리</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}/read</t>
         </is>
@@ -4965,39 +4965,39 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="33" t="inlineStr">
         <is>
           <t>사용자가 알림을 클릭하거나 모두 읽음 처리할 때 read 상태로 변경한다.</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J32" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K32" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L32" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="M32" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-      <c r="P32" s="11" t="inlineStr">
+      <c r="N32" s="33" t="n"/>
+      <c r="O32" s="33" t="n"/>
+      <c r="P32" s="33" t="inlineStr">
         <is>
           <t>{
   "notification_id": 12,
@@ -5006,52 +5006,52 @@
 }</t>
         </is>
       </c>
-      <c r="Q32" s="11" t="inlineStr">
+      <c r="Q32" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 알림 없음</t>
         </is>
       </c>
-      <c r="R32" s="11" t="inlineStr">
+      <c r="R32" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="S32" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백)</t>
         </is>
       </c>
-      <c r="T32" s="27" t="inlineStr">
+      <c r="T32" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1" s="26">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>알림</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}</t>
         </is>
@@ -5061,61 +5061,61 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="33" t="inlineStr">
         <is>
           <t>사용자가 개별 알림을 삭제한다.</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J33" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="L33" s="11" t="inlineStr">
+      <c r="L33" s="33" t="inlineStr">
         <is>
           <t>Frontend</t>
         </is>
       </c>
-      <c r="M33" s="11" t="inlineStr">
+      <c r="M33" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-      <c r="P33" s="11" t="inlineStr">
+      <c r="N33" s="33" t="n"/>
+      <c r="O33" s="33" t="n"/>
+      <c r="P33" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "삭제되었습니다."
 }</t>
         </is>
       </c>
-      <c r="Q33" s="11" t="inlineStr">
+      <c r="Q33" s="33" t="inlineStr">
         <is>
           <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 알림 없음</t>
         </is>
       </c>
-      <c r="R33" s="11" t="inlineStr">
+      <c r="R33" s="33" t="inlineStr">
         <is>
           <t>notifications</t>
         </is>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="33" t="inlineStr">
         <is>
           <t>⭐ v2 신규 (멘토 피드백)</t>
         </is>
       </c>
-      <c r="T33" s="27" t="inlineStr">
+      <c r="T33" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -6509,17 +6509,19 @@
       <c r="O47" s="18" t="inlineStr">
         <is>
           <t>{
-  "medication_alarm": true,
-  "challenge_alarm": true,
   "guide_complete_alarm": true,
-  "push_permission": true
+  "ocr_complete_alarm": true,
+  "system_alarm": true
 }</t>
         </is>
       </c>
       <c r="P47" s="18" t="inlineStr">
         <is>
           <t>{
-  "updated_at": "2026-05-08T17:00:00"
+  "guide_complete_alarm": true,
+  "ocr_complete_alarm": true,
+  "system_alarm": true,
+  "updated_at": "2026-06-04T13:00:00Z"
 }</t>
         </is>
       </c>
@@ -6941,30 +6943,30 @@
       </c>
     </row>
     <row r="52" ht="180" customHeight="1" s="26">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
@@ -6974,38 +6976,38 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="H52" s="33" t="inlineStr">
         <is>
           <t>사용자가 마이페이지에서 비밀번호를 변경한다. 현재 비밀번호 확인 후 새 비밀번호로 변경. 변경 성공 시 모든 기기에서 로그아웃 처리.</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J52" s="11" t="inlineStr">
+      <c r="J52" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="K52" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="L52" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr">
+      <c r="M52" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N52" s="11" t="n"/>
-      <c r="O52" s="11" t="inlineStr">
+      <c r="N52" s="33" t="n"/>
+      <c r="O52" s="33" t="inlineStr">
         <is>
           <t>{
   "current_password": "OldP@ssw0rd1",
@@ -7013,7 +7015,7 @@
 }</t>
         </is>
       </c>
-      <c r="P52" s="11" t="inlineStr">
+      <c r="P52" s="33" t="inlineStr">
         <is>
           <t>{
   "detail": "비밀번호가 변경되었습니다. 다시 로그인해주세요.",
@@ -7021,54 +7023,54 @@
 }</t>
         </is>
       </c>
-      <c r="Q52" s="11" t="inlineStr">
+      <c r="Q52" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 입력 오류 (정책 미충족, 현재 비밀번호와 동일)
 401 현재 비밀번호 불일치</t>
         </is>
       </c>
-      <c r="R52" s="11" t="inlineStr">
+      <c r="R52" s="33" t="inlineStr">
         <is>
           <t>users, auth_tokens</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001). 정책: 8자 이상 20자 이하, 영문 대소문자/숫자/특수문자 중 3종류 이상. ⭐ v3 업데이트: 4단계 흐름 (현재 비밀번호 → 새 비밀번호 → 확인 → 완료). 현재 비밀번호 5회 실패 시 10분 제한. 이메일·이름·닉네임과 동일하면 변경 제한. 변경 성공 시 모든 refresh_token revoke (전체 기기 강제 로그아웃)</t>
         </is>
       </c>
-      <c r="T52" s="27" t="inlineStr">
+      <c r="T52" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="53" ht="180" customHeight="1" s="26">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="33" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D53" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
@@ -7078,39 +7080,39 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="H53" s="33" t="inlineStr">
         <is>
           <t>사용자가 가입 시 동의한 약관·개인정보 처리방침·민감 건강정보 수집·AI 분석 활용·마케팅 등 동의 내역을 조회한다.</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I53" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J53" s="11" t="inlineStr">
+      <c r="J53" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="K53" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L53" s="11" t="inlineStr">
+      <c r="L53" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr">
+      <c r="M53" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N53" s="11" t="n"/>
-      <c r="O53" s="11" t="n"/>
-      <c r="P53" s="11" t="inlineStr">
+      <c r="N53" s="33" t="n"/>
+      <c r="O53" s="33" t="n"/>
+      <c r="P53" s="33" t="inlineStr">
         <is>
           <t>{
   "consents": [
@@ -7148,53 +7150,53 @@
 }</t>
         </is>
       </c>
-      <c r="Q53" s="11" t="inlineStr">
+      <c r="Q53" s="33" t="inlineStr">
         <is>
           <t>200 OK
 401 인증 실패</t>
         </is>
       </c>
-      <c r="R53" s="11" t="inlineStr">
+      <c r="R53" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="S53" s="11" t="inlineStr">
+      <c r="S53" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001). 마이페이지 &gt; 약관 동의 내역 화면용. 5개 약관 (terms, privacy, health_data, ai_analysis, marketing) 각각 상태·동의 일시 반환. 각 약관마다 "전문 보기" 링크 제공</t>
         </is>
       </c>
-      <c r="T53" s="27" t="inlineStr">
+      <c r="T53" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="54" ht="199.5" customHeight="1" s="26">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="33" t="inlineStr">
         <is>
           <t>마이페이지</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>약관 동의 토글 (선택 약관)</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents/{consent_type}</t>
         </is>
@@ -7204,49 +7206,49 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="H54" s="11" t="inlineStr">
+      <c r="H54" s="33" t="inlineStr">
         <is>
           <t>사용자가 마이페이지에서 선택 약관(현재 marketing만 해당)의 동의/철회를 토글한다. 필수 약관(terms, privacy, health_data, ai_analysis)은 본 API로 변경 불가. 필수 약관 철회는 회원탈퇴(DELETE /users/me)를 통해서만 가능.</t>
         </is>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="I54" s="33" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="J54" s="11" t="inlineStr">
+      <c r="J54" s="33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K54" s="11" t="inlineStr">
+      <c r="K54" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
-      <c r="L54" s="11" t="inlineStr">
+      <c r="L54" s="33" t="inlineStr">
         <is>
           <t>Frontend · 조이레</t>
         </is>
       </c>
-      <c r="M54" s="11" t="inlineStr">
+      <c r="M54" s="33" t="inlineStr">
         <is>
           <t>Authorization: Bearer {access_token}</t>
         </is>
       </c>
-      <c r="N54" s="11" t="inlineStr">
+      <c r="N54" s="33" t="inlineStr">
         <is>
           <t>path: consent_type (marketing)</t>
         </is>
       </c>
-      <c r="O54" s="11" t="inlineStr">
+      <c r="O54" s="33" t="inlineStr">
         <is>
           <t>{
   "is_agreed": true
 }</t>
         </is>
       </c>
-      <c r="P54" s="11" t="inlineStr">
+      <c r="P54" s="33" t="inlineStr">
         <is>
           <t>{
   "consent_type": "marketing",
@@ -7256,7 +7258,7 @@
 }</t>
         </is>
       </c>
-      <c r="Q54" s="11" t="inlineStr">
+      <c r="Q54" s="33" t="inlineStr">
         <is>
           <t>200 OK
 400 필수 약관은 본 API로 변경 불가 ("필수 약관 철회는 회원탈퇴를 진행해주세요")
@@ -7264,17 +7266,17 @@
 404 존재하지 않는 consent_type</t>
         </is>
       </c>
-      <c r="R54" s="11" t="inlineStr">
+      <c r="R54" s="33" t="inlineStr">
         <is>
           <t>user_consents</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr">
+      <c r="S54" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (REQ-MYPAGE-001 자세히 작성). 마케팅 수신 동의 토글용. 필수 약관(terms·privacy·health_data·ai_analysis)은 400 응답 후 회원탈퇴 안내</t>
         </is>
       </c>
-      <c r="T54" s="27" t="inlineStr">
+      <c r="T54" s="34" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -9264,52 +9266,52 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>순번</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>기능명</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9319,32 +9321,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/signup</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>회원가입 및 필수 동의 저장</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9354,32 +9356,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/login</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>로그인 및 토큰 발급</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9389,32 +9391,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>/api/v1/auth/logout</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="33" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9424,32 +9426,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>내 정보 조회</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9459,32 +9461,32 @@
           <t>PUT</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 저장/수정</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9494,32 +9496,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>/api/v1/health-profile</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>간단 건강정보 조회</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9529,32 +9531,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="33" t="inlineStr">
         <is>
           <t>의료 이미지 업로드</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9564,32 +9566,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="33" t="inlineStr">
         <is>
           <t>진료기록 목록 조회</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9599,32 +9601,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="33" t="inlineStr">
         <is>
           <t>진료기록 상세 조회</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9634,32 +9636,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>/api/v1/ocr/jobs</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="33" t="inlineStr">
         <is>
           <t>OCR 작업 시작</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9669,32 +9671,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-result</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 조회</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9704,32 +9706,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/ocr-text</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="33" t="inlineStr">
         <is>
           <t>OCR 결과 수정</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9739,32 +9741,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="33" t="inlineStr">
         <is>
           <t>/api/v1/medications/{medication_id}/verify</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="33" t="inlineStr">
         <is>
           <t>OCR 약품명 확인</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9774,32 +9776,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/search</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="33" t="inlineStr">
         <is>
           <t>식약처 약품 검색</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9809,32 +9811,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>/api/v1/drugs/{drug_id}</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="33" t="inlineStr">
         <is>
           <t>약품 상세 조회</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9844,32 +9846,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/medications</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="33" t="inlineStr">
         <is>
           <t>기록별 약품 목록 조회</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9879,32 +9881,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="33" t="inlineStr">
         <is>
           <t>LLM 복약/생활습관 가이드 생성</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9914,32 +9916,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="33" t="inlineStr">
         <is>
           <t>/api/v1/guides/{guide_id}</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="33" t="inlineStr">
         <is>
           <t>가이드 상세 조회</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9949,32 +9951,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="33" t="inlineStr">
         <is>
           <t>/api/v1/records/{record_id}/guide</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="33" t="inlineStr">
         <is>
           <t>기록별 최신 가이드 조회</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -9984,32 +9986,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="33" t="inlineStr">
         <is>
           <t>상담 세션 생성</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10019,32 +10021,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="33" t="inlineStr">
         <is>
           <t>상담 세션 목록 조회</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10054,32 +10056,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="33" t="inlineStr">
         <is>
           <t>상담 메시지 목록 조회</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="26">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10089,32 +10091,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="33" t="inlineStr">
         <is>
           <t>/api/v1/chat/sessions/{session_id}/messages</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="33" t="inlineStr">
         <is>
           <t>챗봇 메시지 전송 및 답변 생성</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="26">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10124,32 +10126,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="33" t="inlineStr">
         <is>
           <t>/api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="33" t="inlineStr">
         <is>
           <t>비동기 작업 상태 조회</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C29" s="11" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10159,32 +10161,32 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="33" t="inlineStr">
         <is>
           <t>/api/v1/feedbacks</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="33" t="inlineStr">
         <is>
           <t>복약 가이드 피드백 단순 등록</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>Backend B</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10194,32 +10196,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="33" t="inlineStr">
         <is>
           <t>알림 목록 조회</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="33" t="inlineStr">
         <is>
           <t>Backend A/B</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10229,32 +10231,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/unread-count</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="33" t="inlineStr">
         <is>
           <t>미읽음 알림 개수 조회</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="33" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10264,32 +10266,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}/read</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>알림 읽음 처리</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="26">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="33" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C33" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10299,17 +10301,17 @@
           <t>DELETE</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="33" t="inlineStr">
         <is>
           <t>/api/v1/notifications/{notification_id}</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="33" t="inlineStr">
         <is>
           <t>알림 삭제</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="33" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
@@ -10946,15 +10948,15 @@
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="26">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="33" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B52" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C52" s="11" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10964,32 +10966,32 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E52" s="11" t="inlineStr">
+      <c r="E52" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/password</t>
         </is>
       </c>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="F52" s="33" t="inlineStr">
         <is>
           <t>비밀번호 변경 ⭐ v3</t>
         </is>
       </c>
-      <c r="G52" s="11" t="inlineStr">
+      <c r="G52" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="26">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="33" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
+      <c r="C53" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -10999,32 +11001,32 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E53" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F53" s="33" t="inlineStr">
         <is>
           <t>약관 동의 내역 조회 ⭐ v3</t>
         </is>
       </c>
-      <c r="G53" s="11" t="inlineStr">
+      <c r="G53" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="26">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="33" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="11" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
         <is>
           <t>Sprint 2 필수 MVP</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="33" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -11034,17 +11036,17 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
+      <c r="E54" s="33" t="inlineStr">
         <is>
           <t>/api/v1/users/me/consents/{consent_type}</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="F54" s="33" t="inlineStr">
         <is>
           <t>약관 동의 토글 (선택 약관) ⭐ v3</t>
         </is>
       </c>
-      <c r="G54" s="11" t="inlineStr">
+      <c r="G54" s="33" t="inlineStr">
         <is>
           <t>Backend A · 돈유정</t>
         </is>
@@ -12035,84 +12037,84 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>규칙 / 정책</t>
         </is>
       </c>
     </row>
     <row r="5" ht="49.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>Base URL</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>/api/v1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>인증 방식</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Bearer Token (JWT). Authorization: Bearer {access_token} 헤더로 전달.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>토큰 정책</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>access_token 유효기간 1시간, refresh_token 유효기간 14일. 5회 연속 로그인 실패 시 10분 잠금.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="49.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>Content-Type</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>기본 application/json. 파일 업로드는 multipart/form-data.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="49.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>요청·응답 인코딩</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>UTF-8</t>
         </is>
       </c>
     </row>
     <row r="10" ht="252" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>⭐ 상태코드 정책 v2</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>멘토 피드백 반영: 400으로 통일. 422 사용하지 않음. 
 • 200 OK: 조회·수정 성공
@@ -12132,12 +12134,12 @@
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>⭐ LLM 실패 처리 v2</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>멘토 피드백 반영: "500 LLM 실패" 별도 항목 사용하지 않음.
 • LLM 생성 실패 → processing_jobs.status = 'failed' + error_message 저장
@@ -12148,12 +12150,12 @@
       </c>
     </row>
     <row r="12" ht="54" customHeight="1" s="26">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>⭐ 비동기 작업 응답</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>OCR·LLM은 동기 응답 대신 202 Accepted + job_id 반환.
 클라이언트는 GET /processing-jobs/{job_id}로 상태 폴링.
@@ -12162,12 +12164,12 @@
       </c>
     </row>
     <row r="13" ht="72" customHeight="1" s="26">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>타임아웃 정책</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>• OCR Job: 60초
 • LLM Job: 90초
@@ -12177,12 +12179,12 @@
       </c>
     </row>
     <row r="14" ht="72" customHeight="1" s="26">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>⭐ 식약처 API 출처</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>공공데이터포털 - 식품의약품안전처 의약품 제품 허가 정보
 https://www.data.go.kr/data/15095677/openapi.do
@@ -12192,36 +12194,36 @@
       </c>
     </row>
     <row r="15" ht="49.5" customHeight="1" s="26">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>페이지네이션</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>조회 API는 ?page={n}&amp;size={n} 또는 ?offset={n}&amp;limit={n} 쿼리 파라미터 지원. (챗봇 상담 목록 등은 offset/limit 적용)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="49.5" customHeight="1" s="26">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>요청 검증</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>필수값 누락·타입 오류·비즈니스 검증 실패는 모두 400으로 통일. detail 필드에 사용자에게 표시 가능한 메시지 포함.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="72" customHeight="1" s="26">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>페이로드 검증 예시</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>{
   "detail": "이미 가입된 이메일입니다.",
@@ -12231,48 +12233,48 @@
       </c>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="26">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>민감정보 마스킹</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>로그·에러 응답에 OCR 원문·건강정보·토큰·API Key 노출 금지. 마스킹 또는 출력 제외 처리.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="49.5" customHeight="1" s="26">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>사용자 데이터 격리</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>모든 인증 API는 토큰의 user_id와 리소스의 user_id 검증. 타 사용자 접근 시 403 또는 404 반환.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="49.5" customHeight="1" s="26">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Rate Limit (예정)</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Sprint 3에서 도입 검토. 챗봇 메시지 등 비용 부담 API는 429 응답 + Retry-After 헤더.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="49.5" customHeight="1" s="26">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>API 버전 관리</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="36" t="inlineStr">
         <is>
           <t>URL 경로에 버전 명시 (/api/v1/...). 호환성 깨지는 변경 시 /v2/ 추가.</t>
         </is>
@@ -13300,259 +13302,259 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>작업 유형</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>트리거 API</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>상태 조회 API</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>타임아웃</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="35" t="inlineStr">
         <is>
           <t>성공 시</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="35" t="inlineStr">
         <is>
           <t>실패 시</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>OCR 처리</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/ocr/jobs</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>60초</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="36" t="inlineStr">
         <is>
           <t>status=completed → ocr_text·medications 후보 저장</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>status=failed 또는 timeout → 사용자에게 재시도 또는 직접 입력 안내</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>식약처 약품 조회</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search (동기 + 캐시)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>(N/A - 동기)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
         <is>
           <t>drug_references 저장 + drug_caches 갱신</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>drug_caches 있으면 캐시 반환 + 마지막 조회 시각 표시 / 없으면 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>LLM 가이드 생성</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/guides</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>90초</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>status=completed → guides·guide_items 저장 + 알림 생성</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>status=failed → 사용자에게 재시도 안내 + 알림 생성</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>챗봇 메시지</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions/{id}/messages (동기, 5초 목표)</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>(N/A - 동기)</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>ssistant_message 즉시 응답 + safety_flag 평가</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>status=failed 응답 + 사용자에게 "답변 생성 실패" 안내</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>RAG 임베딩 (Sprint 3)</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/guideline-sources</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>120초</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>guideline_chunks + embedding_vector 저장</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>embedding_status=failed → 운영자 재시도</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>FHIR 연동 (상용화)</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/fhir/connections</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/processing-jobs/{job_id}</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>30초</t>
         </is>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>fhir_connections.connection_status=connected</t>
         </is>
       </c>
-      <c r="G10" s="25" t="inlineStr">
+      <c r="G10" s="36" t="inlineStr">
         <is>
           <t>502 Bad Gateway + retry_count 증가</t>
         </is>
@@ -14573,447 +14575,447 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>평가요건</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>요구사항 ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="35" t="inlineStr">
         <is>
           <t>관련 API</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>산출물 위치</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="4" ht="49.5" customHeight="1" s="26">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>1-1. LLM 기반 안내 가이드 생성</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>REQ-GUIDE-001/002</t>
         </is>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="36" t="inlineStr">
         <is>
           <t>POST /guides, GET /guides/{guide_id}</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="36" t="inlineStr">
         <is>
           <t>guides·guide_items 테이블, 가이드 결과 화면</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>복약 + 생활습관 가이드 + 의료 안전 고지</t>
         </is>
       </c>
     </row>
     <row r="5" ht="49.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1-2. RAG 파이프라인 (공식협회 기반)</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>REQ-RAG-PILOT-001 / REQ-RAG-001</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>POST /guideline-sources, GET /guideline-sources/search</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>guideline_sources·chunks 테이블</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 파일럿 → Sprint 3 pgvector 고도화</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2-1. 실시간 챗봇 (맥락 반영)</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>REQ-CHAT-001/002</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions, POST /chat/sessions/{id}/messages, GET /chat/sessions/{id}/messages</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>chat_sessions·messages 테이블</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>최근 3~5개 메시지 context 포함</t>
         </is>
       </c>
     </row>
     <row r="7" ht="49.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>2-2. 챗봇 위험 질문 안전 응답</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>REQ-CHAT-003 / REQ-SAFE-001</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>POST /chat/sessions/{id}/messages (safety_flag)</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>chat_messages.safety_flag</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>키워드 기반 1차 감지 + 상시 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="8" ht="49.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>3-1. OCR 기반 의료정보 인식</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001/002</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>POST /ocr/jobs, GET /processing-jobs/{job_id}, GET /records/{id}/ocr-result</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>medical_records·processing_jobs</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Upstage OCR + 라인 단위 저장</t>
         </is>
       </c>
     </row>
     <row r="9" ht="49.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>3-2. OCR 결과 사용자 검수</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-002</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>PATCH /records/{id}/ocr-text, PATCH /medications/{id}/verify</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>medications.is_verified</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>신뢰도 70% 미만 강조</t>
         </is>
       </c>
     </row>
     <row r="10" ht="49.5" customHeight="1" s="26">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>3-3. 복약알림 (필수 MVP)</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>REQ-NOTI-001</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>GET /notifications, GET /notifications/unread-count, PATCH /notifications/{id}/read, DELETE /notifications/{id}</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>notifications 테이블</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>⭐ v2 P0 상향 (내부 알림함)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="49.5" customHeight="1" s="26">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>3-4. 피드백 수집 (필수 MVP)</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>REQ-FB-001</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>POST /feedbacks</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>feedbacks 테이블</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>⭐ v2 P0 상향 (가이드·챗봇 피드백)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="49.5" customHeight="1" s="26">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>4-1. 사용자 데이터 접근 제어</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>REQ-SEC-001</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>전체 인증 필요 API</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>user_id 검증 미들웨어</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n"/>
+      <c r="E12" s="36" t="n"/>
     </row>
     <row r="13" ht="49.5" customHeight="1" s="26">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>4-2. 민감정보 보호·로그 마스킹</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>REQ-SEC-002</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>(전체)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>로그 정책 문서</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n"/>
+      <c r="E13" s="36" t="n"/>
     </row>
     <row r="14" ht="49.5" customHeight="1" s="26">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>5-1. API 성능 측정 (P95)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>REQ-NF-002</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>주요 조회 API</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>API 성능 테스트 문서</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>P95 3초 목표</t>
         </is>
       </c>
     </row>
     <row r="15" ht="49.5" customHeight="1" s="26">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>5-2. 비동기 처리</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>REQ-NF-001</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>POST /ocr/jobs, POST /guides, GET /processing-jobs/{id}</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>processing_jobs 테이블</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>타임아웃 관리 포함</t>
         </is>
       </c>
     </row>
     <row r="16" ht="49.5" customHeight="1" s="26">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>5-3. 식약처 API 연동</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/search, GET /drugs/{id}</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>drug_references·drug_caches·api_failure_logs</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>⭐ 공공데이터포털 링크 명시</t>
         </is>
       </c>
     </row>
     <row r="17" ht="49.5" customHeight="1" s="26">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>6-1. 핵심 플로우 (3~5단계)</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>REQ-UX-001</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>전체 화면 흐름</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>와이어프레임 #01~#18 + User Flow</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n"/>
+      <c r="E17" s="36" t="n"/>
     </row>
     <row r="18" ht="49.5" customHeight="1" s="26">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>6-2. 협업·문서화</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>REQ-DOC-001</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>(N/A - 문서)</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>R&amp;R, Git, ERD, API 명세서 v2, 와이어프레임</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>Git 브랜치 전략 4개</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>3-5. 마이페이지 (계정 관리) ⭐</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 ⭐ v3</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>GET/PATCH /users/me, PATCH password, DELETE /users/me, GET /users/me/consents</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="33" t="inlineStr">
         <is>
           <t>users 테이블 + user_consents + auth_tokens</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="33" t="inlineStr">
         <is>
           <t>⭐ v3 신규 (팀원 피드백)</t>
         </is>
@@ -16039,132 +16041,132 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>핵심 범위 (Sprint 2 MVP)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>Git 브랜치</t>
         </is>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1" s="26">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>돈유정</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Backend A</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>회원가입/로그인/JWT, 사용자/건강 프로필, 의료 문서 업로드, OCR 작업 생성/조회/수정, processing_jobs 상태 조회, 알림 API (P0 상향)</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>feature/backend-auth-ocr</t>
         </is>
       </c>
     </row>
     <row r="6" ht="79.5" customHeight="1" s="26">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>신정호</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Backend B (RAG 파이프라인 중심)</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>식약처 API 약품 검색·후보 선택, 챗봇 API, 위험 질문 감지, API 명세서 최신화, 공식협회 기반 RAG 흐름 연결, 피드백 등록 (P0 상향)</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>feature/backend-guide-chat</t>
         </is>
       </c>
     </row>
     <row r="7" ht="79.5" customHeight="1" s="26">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>조이레</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>Frontend + 총괄</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>반응형 웹 화면 전체 (#01~#18), 와이어프레임 기반 UI 구현, API 연결, 알림함·피드백 UI</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>feature/frontend-responsive-web</t>
         </is>
       </c>
     </row>
     <row r="8" ht="79.5" customHeight="1" s="26">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>이정훈</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>AI/Infra + 배포</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>OCR API 테스트/구현, LLM 프롬프트 작성, 복약/생활습관 가이드 생성, 챗봇 안전 응답 프롬프트, 위험 질문 키워드, 공통 에러/테스트 케이스, 배포</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>feature/ai-prompt-test</t>
         </is>
       </c>
     </row>
     <row r="9" ht="79.5" customHeight="1" s="26">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>유태영</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>멘토</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>기획 리뷰·피드백·평가 항목 점검</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>(N/A)</t>
         </is>
@@ -17192,459 +17194,459 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="35" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>상태코드 정책</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>400 / 422 입력값 검증 실패 구분</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>400으로 통일 (모든 입력 오류 포함)</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>멘토: 토스 개발자 센터 참고</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>LLM 실패 처리</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>POST /chat/messages → 500 LLM 실패</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>※ LLM 실패는 job status=failed로 처리 (HTTP 상태가 아닌 비즈니스 상태)</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>멘토: 500 LLM 실패 항목 삭제</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>POST /records 응답</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>500 저장 실패 포함</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>500 저장 실패 제거 (서버 내부 오류로 일반화)</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>상태코드 정리</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>/api/v1/admin/operation-logs</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>P3 상용화 검토에 포함</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>API 명세에서 완전 삭제</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>멘토: 운영 로그는 ERD 내부 검토만</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/notifications</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>Sprint 3 P2</t>
         </is>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>멘토: 복약알림 필수 MVP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>POST /api/v1/feedbacks</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 Stretch P1</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>멘토: 피드백 필수 MVP</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/notifications/unread-count</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="36" t="inlineStr">
         <is>
           <t>대시보드 알림 뱃지 (멘토: 알림 디테일)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>PATCH /api/v1/notifications/{id}/read</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="36" t="inlineStr">
         <is>
           <t>내부 알림함 (멘토 피드백)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>DELETE /api/v1/notifications/{id}</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>내부 알림함 (멘토 피드백)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/search 비고</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="36" t="inlineStr">
         <is>
           <t>"식약처 API 호출"</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="36" t="inlineStr">
         <is>
           <t>+ 공공데이터포털 URL 추가</t>
         </is>
       </c>
-      <c r="E14" s="25" t="inlineStr">
+      <c r="E14" s="36" t="inlineStr">
         <is>
           <t>멘토: 식약처 API 데이터셋 링크</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>GET /api/v1/drugs/{drug_id} 비고</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="36" t="inlineStr">
         <is>
           <t>기본 설명</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="36" t="inlineStr">
         <is>
           <t>+ 제조사 정보 포함 응답 명시</t>
         </is>
       </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="E15" s="36" t="inlineStr">
         <is>
           <t>멘토: 제조사 다른 경우 표시</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>/api/v1/challenge-checkins</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="36" t="inlineStr">
         <is>
           <t>Sprint 3 P2</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="36" t="inlineStr">
         <is>
           <t>확인 완료 — Sprint 3 P2 유지</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="36" t="inlineStr">
         <is>
           <t>멘토: 확인 요청 답변</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>공통 규칙 시트</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>기본 규칙만</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="36" t="inlineStr">
         <is>
           <t>+ 상태코드 정책, LLM 실패 처리, 식약처 출처 추가</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>v2 전체 정책 통일</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>20개 시트</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="36" t="inlineStr">
         <is>
           <t>8개 시트로 통합</t>
         </is>
       </c>
-      <c r="E18" s="25" t="inlineStr">
+      <c r="E18" s="36" t="inlineStr">
         <is>
           <t>도메인별 분리 시트들을 우선순위로 통합</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Sprint 우선순위 분류</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Sprint2_MVP_P0, Sprint2_Stretch_P1, Sprint3_P2, Commercial_P3 4개 시트</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="36" t="inlineStr">
         <is>
           <t>1개 시트로 통합 (단계 컬럼 필터)</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E19" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>도메인별 시트</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>회원_사용자, 기록_OCR, 약품_가이드, 챗봇_작업상태, Sprint3_확장, 상용화_검토 6개 시트</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="36" t="inlineStr">
         <is>
           <t>전체 명세 시트의 도메인 컬럼으로 대체</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E20" s="36" t="inlineStr">
         <is>
           <t>시트 정리</t>
         </is>
@@ -17659,270 +17661,270 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Before (v2)</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>After (v3)</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="26">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E24" s="25" t="inlineStr">
+      <c r="E24" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="26">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>신규 추가 Sprint 2 P0</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E25" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="36" t="inlineStr">
         <is>
           <t>POST /auth/login 비고</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>+ 통합 메시지 응답 명시 (계정 존재 노출 방지)</t>
         </is>
       </c>
-      <c r="E26" s="25" t="inlineStr">
+      <c r="E26" s="36" t="inlineStr">
         <is>
           <t>REQ-AUTH-002 (팀원 보안 피드백)</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="26">
-      <c r="A27" s="25" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>GET /records/{id}/ocr 비고</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>+ medications[].manufacturer 필수 명시</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="E27" s="36" t="inlineStr">
         <is>
           <t>REQ-OCR-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="26">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/search 비고</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>식약처 API 호출</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>+ manufacturer 필수 필드 ("제조사 정보 없음" 폴백)</t>
         </is>
       </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="E28" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="26">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="36" t="inlineStr">
         <is>
           <t>GET /drugs/{id} 비고</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="36" t="inlineStr">
         <is>
           <t>기본 비고</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>+ manufacturer 필수 필드 명시</t>
         </is>
       </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="E29" s="36" t="inlineStr">
         <is>
           <t>REQ-DRUG-001 (팀원 피드백)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="26">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>POST /records 비고</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>image_expires_at 90일 보존</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>+ REQ-REC-001과 일치 확인 완료 추가</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="36" t="inlineStr">
         <is>
           <t>팀원 피드백: 요구사항·API 일치 확인</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="26">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>전체 API 수</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>47개</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="36" t="inlineStr">
         <is>
           <t>49개 (+2 마이페이지)</t>
         </is>
       </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="E31" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 신규</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="26">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>Sprint 2 P0 API 수</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>29개</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="36" t="inlineStr">
         <is>
           <t>31개 (+2 마이페이지)</t>
         </is>
       </c>
-      <c r="E32" s="25" t="inlineStr">
+      <c r="E32" s="36" t="inlineStr">
         <is>
           <t>마이페이지 P0</t>
         </is>
@@ -17937,216 +17939,216 @@
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="26">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>변경 영역</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>사유</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="26">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B36" s="36" t="inlineStr">
         <is>
           <t>REQ-MYPAGE-001 상세 요구사항</t>
         </is>
       </c>
-      <c r="C36" s="25" t="inlineStr">
+      <c r="C36" s="36" t="inlineStr">
         <is>
           <t>7개 메뉴 간단 나열</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="36" t="inlineStr">
         <is>
           <t>10개 메뉴 + 비밀번호 변경 4단계 + 회원탈퇴 5단계 + 약관 5개 관리 상세</t>
         </is>
       </c>
-      <c r="E36" s="25" t="inlineStr">
+      <c r="E36" s="36" t="inlineStr">
         <is>
           <t>팀원: 마이페이지 자세히 작성</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="26">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B37" s="25" t="inlineStr">
+      <c r="B37" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/password 비고</t>
         </is>
       </c>
-      <c r="C37" s="25" t="inlineStr">
+      <c r="C37" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D37" s="25" t="inlineStr">
+      <c r="D37" s="36" t="inlineStr">
         <is>
           <t>+ 4단계 흐름, 5회 실패 10분 제한, 이메일·이름·닉네임 동일 제한</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="E37" s="36" t="inlineStr">
         <is>
           <t>비밀번호 변경 상세화</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="26">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="36" t="inlineStr">
         <is>
           <t>DELETE /users/me 비고</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C38" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D38" s="36" t="inlineStr">
         <is>
           <t>+ 5단계 흐름, 5회 실패 24시간 제한, OCR/LLM cancelled, 30일 영구 삭제 배치</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="36" t="inlineStr">
         <is>
           <t>회원탈퇴 상세화</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="26">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B39" s="36" t="inlineStr">
         <is>
           <t>GET /users/me/consents 비고</t>
         </is>
       </c>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C39" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D39" s="25" t="inlineStr">
+      <c r="D39" s="36" t="inlineStr">
         <is>
           <t>+ 5개 약관 (terms/privacy/health_data/ai_analysis/marketing), 전문 보기</t>
         </is>
       </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="E39" s="36" t="inlineStr">
         <is>
           <t>약관 관리 상세화</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="26">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="A40" s="36" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me 비고</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C40" s="36" t="inlineStr">
         <is>
           <t>기본</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="36" t="inlineStr">
         <is>
           <t>+ 30일 1회 변경 제한, 욕설 필터링, 다음 변경 가능일 메시지</t>
         </is>
       </c>
-      <c r="E40" s="25" t="inlineStr">
+      <c r="E40" s="36" t="inlineStr">
         <is>
           <t>닉네임 정책 명시</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="26">
-      <c r="A41" s="25" t="inlineStr">
+      <c r="A41" s="36" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="36" t="inlineStr">
         <is>
           <t>PATCH /users/me/consents/{type}</t>
         </is>
       </c>
-      <c r="C41" s="25" t="inlineStr">
+      <c r="C41" s="36" t="inlineStr">
         <is>
           <t>(없음)</t>
         </is>
       </c>
-      <c r="D41" s="25" t="inlineStr">
+      <c r="D41" s="36" t="inlineStr">
         <is>
           <t>신규 추가 (선택 약관 토글, 필수 약관은 400)</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E41" s="36" t="inlineStr">
         <is>
           <t>마케팅 수신 토글용</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="26">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="36" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="36" t="inlineStr">
         <is>
           <t>전체 API 개수</t>
         </is>
       </c>
-      <c r="C42" s="25" t="inlineStr">
+      <c r="C42" s="36" t="inlineStr">
         <is>
           <t>49개</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="36" t="inlineStr">
         <is>
           <t>50개 (+1)</t>
         </is>
       </c>
-      <c r="E42" s="25" t="inlineStr">
+      <c r="E42" s="36" t="inlineStr">
         <is>
           <t>약관 토글 추가</t>
         </is>

--- a/docs/api/api-spec-final.xlsx
+++ b/docs/api/api-spec-final.xlsx
@@ -3046,7 +3046,17 @@
   "record_id": 10,
   "record_type": "prescription",
   "status": "ocr_completed",
-  "ocr_confidence": 0.91
+  "file_url": "https://.../rx.png",
+  "file_name": "처방전.png",
+  "file_size": 123456,
+  "content_type": "image/png",
+  "ocr_text": "...",
+  "ocr_edited_text": null,
+  "ocr_confidence": 0.91,
+  "input_method": "upload",
+  "image_expires_at": "2026-09-01T00:00:00Z",
+  "uploaded_at": "2026-06-04T10:00:00Z",
+  "updated_at": "2026-06-04T10:05:00Z"
 }</t>
         </is>
       </c>
@@ -3777,12 +3787,12 @@
       </c>
       <c r="S20" s="33" t="inlineStr">
         <is>
-          <t>⭐ v4: 미구현 — ocr-result의 medication_candidates로 대체 추정 (확인 필요)</t>
+          <t>구현 완료 (Backend B). 응답 {record_id, medications:[{medication_id, drug_name, dosage, frequency, timing, duration, is_verified, ...}]}</t>
         </is>
       </c>
       <c r="T20" s="28" t="inlineStr">
         <is>
-          <t>미구현 (확인필요)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -4082,12 +4092,12 @@
       </c>
       <c r="S23" s="33" t="inlineStr">
         <is>
-          <t>⭐ v4: 미구현 — GET /guides/{guide_id}로 대체 (확인 필요)</t>
+          <t>구현 완료 (#104, Backend B). 응답은 GET /guides/{guide_id}와 동일 (GenerateGuideResponse)</t>
         </is>
       </c>
       <c r="T23" s="28" t="inlineStr">
         <is>
-          <t>미구현 (확인필요)</t>
+          <t>완료</t>
         </is>
       </c>
     </row>
@@ -7357,13 +7367,13 @@
       <c r="P55" s="33" t="inlineStr">
         <is>
           <t>{
-  "detail": "인증 코드가 발송되었습니다."
+  "detail": "인증 코드가 이메일로 발송되었습니다."
 }</t>
         </is>
       </c>
       <c r="Q55" s="33" t="inlineStr">
         <is>
-          <t>200 OK / 400 이메일 형식 오류 / 429 발송 쿨다운</t>
+          <t>200 OK / 400 이메일 형식 오류 / 429 발송 쿨다운 (body: {detail, retry_after})</t>
         </is>
       </c>
       <c r="R55" s="33" t="inlineStr">
@@ -7458,7 +7468,7 @@
       <c r="P56" s="33" t="inlineStr">
         <is>
           <t>{
-  "verified": true
+  "detail": "이메일 인증이 완료되었습니다."
 }</t>
         </is>
       </c>
@@ -7956,10 +7966,10 @@
       <c r="P61" s="33" t="inlineStr">
         <is>
           <t>{
-  "medication_alarm": true,
-  "challenge_alarm": true,
   "guide_complete_alarm": true,
-  "push_permission": true
+  "ocr_complete_alarm": true,
+  "system_alarm": true,
+  "updated_at": "2026-06-04T10:00:00Z"
 }</t>
         </is>
       </c>
@@ -8261,14 +8271,12 @@
       <c r="O64" s="33" t="n"/>
       <c r="P64" s="33" t="inlineStr">
         <is>
-          <t>{
-  "detail": "삭제되었습니다."
-}</t>
+          <t>204 No Content (응답 본문 없음)</t>
         </is>
       </c>
       <c r="Q64" s="33" t="inlineStr">
         <is>
-          <t>200 OK / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
+          <t>204 No Content / 401 인증 실패 / 403 권한 없음 / 404 기록 없음</t>
         </is>
       </c>
       <c r="R64" s="33" t="inlineStr">

--- a/docs/api/api-spec-final.xlsx
+++ b/docs/api/api-spec-final.xlsx
@@ -6519,17 +6519,19 @@
       <c r="O47" s="18" t="inlineStr">
         <is>
           <t>{
-  "medication_alarm": true,
-  "challenge_alarm": true,
   "guide_complete_alarm": true,
-  "push_permission": true
+  "ocr_complete_alarm": true,
+  "system_alarm": true
 }</t>
         </is>
       </c>
       <c r="P47" s="18" t="inlineStr">
         <is>
           <t>{
-  "updated_at": "2026-05-08T17:00:00"
+  "guide_complete_alarm": true,
+  "ocr_complete_alarm": true,
+  "system_alarm": true,
+  "updated_at": "2026-06-04T13:00:00Z"
 }</t>
         </is>
       </c>
